--- a/3. outputs/Total return time series/Barkley Sockeye total annual returns by CU_collated.xlsx
+++ b/3. outputs/Total return time series/Barkley Sockeye total annual returns by CU_collated.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:N405"/>
+  <dimension ref="A1:N408"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -4964,24 +4964,50 @@
     </row>
     <row r="112">
       <c r="A112">
-        <v>1921</v>
+        <v>2025</v>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>GCL</t>
+          <t>HUC</t>
+        </is>
+      </c>
+      <c r="C112">
+        <v>15964</v>
+      </c>
+      <c r="E112">
+        <v>4923</v>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>AUC survey - Clemens</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>commercial + FN catch records + creel survey</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>DNA attribution</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr">
+        <is>
+          <t>scale sampling</t>
         </is>
       </c>
       <c r="J112">
         <v>0</v>
       </c>
-      <c r="L112">
-        <v>2688000</v>
+      <c r="K112">
+        <v>0</v>
       </c>
       <c r="M112">
-        <v>325</v>
+        <v>294097</v>
       </c>
       <c r="N112">
-        <v>1000</v>
+        <v>569894</v>
       </c>
     </row>
     <row r="113">
@@ -4990,14 +5016,14 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>SPR</t>
+          <t>GCL</t>
         </is>
       </c>
       <c r="J113">
         <v>0</v>
       </c>
       <c r="L113">
-        <v>1312000</v>
+        <v>2688000</v>
       </c>
       <c r="M113">
         <v>325</v>
@@ -5008,24 +5034,24 @@
     </row>
     <row r="114">
       <c r="A114">
-        <v>1922</v>
+        <v>1921</v>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>GCL</t>
+          <t>SPR</t>
         </is>
       </c>
       <c r="J114">
         <v>0</v>
       </c>
       <c r="L114">
-        <v>1996000</v>
+        <v>1312000</v>
       </c>
       <c r="M114">
-        <v>12350</v>
+        <v>325</v>
       </c>
       <c r="N114">
-        <v>70000</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="115">
@@ -5034,14 +5060,14 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>SPR</t>
+          <t>GCL</t>
         </is>
       </c>
       <c r="J115">
         <v>0</v>
       </c>
       <c r="L115">
-        <v>1456000</v>
+        <v>1996000</v>
       </c>
       <c r="M115">
         <v>12350</v>
@@ -5052,24 +5078,24 @@
     </row>
     <row r="116">
       <c r="A116">
-        <v>1923</v>
+        <v>1922</v>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>GCL</t>
+          <t>SPR</t>
         </is>
       </c>
       <c r="J116">
         <v>0</v>
       </c>
       <c r="L116">
-        <v>2002000</v>
+        <v>1456000</v>
       </c>
       <c r="M116">
-        <v>1456</v>
+        <v>12350</v>
       </c>
       <c r="N116">
-        <v>90000</v>
+        <v>70000</v>
       </c>
     </row>
     <row r="117">
@@ -5078,7 +5104,7 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>SPR</t>
+          <t>GCL</t>
         </is>
       </c>
       <c r="J117">
@@ -5096,24 +5122,24 @@
     </row>
     <row r="118">
       <c r="A118">
-        <v>1924</v>
+        <v>1923</v>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>GCL</t>
+          <t>SPR</t>
         </is>
       </c>
       <c r="J118">
         <v>0</v>
       </c>
       <c r="L118">
-        <v>1094800</v>
+        <v>2002000</v>
       </c>
       <c r="M118">
-        <v>2964</v>
+        <v>1456</v>
       </c>
       <c r="N118">
-        <v>120000</v>
+        <v>90000</v>
       </c>
     </row>
     <row r="119">
@@ -5122,14 +5148,14 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>SPR</t>
+          <t>GCL</t>
         </is>
       </c>
       <c r="J119">
         <v>0</v>
       </c>
       <c r="L119">
-        <v>2002000</v>
+        <v>1094800</v>
       </c>
       <c r="M119">
         <v>2964</v>
@@ -5140,11 +5166,11 @@
     </row>
     <row r="120">
       <c r="A120">
-        <v>1925</v>
+        <v>1924</v>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>GCL</t>
+          <t>SPR</t>
         </is>
       </c>
       <c r="J120">
@@ -5154,10 +5180,10 @@
         <v>2002000</v>
       </c>
       <c r="M120">
-        <v>16081</v>
+        <v>2964</v>
       </c>
       <c r="N120">
-        <v>80000</v>
+        <v>120000</v>
       </c>
     </row>
     <row r="121">
@@ -5166,7 +5192,7 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>SPR</t>
+          <t>GCL</t>
         </is>
       </c>
       <c r="J121">
@@ -5184,19 +5210,11 @@
     </row>
     <row r="122">
       <c r="A122">
-        <v>1926</v>
+        <v>1925</v>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>GCL</t>
-        </is>
-      </c>
-      <c r="C122">
-        <v>10695</v>
-      </c>
-      <c r="F122" t="inlineStr">
-        <is>
-          <t>manual transport count</t>
+          <t>SPR</t>
         </is>
       </c>
       <c r="J122">
@@ -5206,10 +5224,10 @@
         <v>2002000</v>
       </c>
       <c r="M122">
-        <v>45412</v>
+        <v>16081</v>
       </c>
       <c r="N122">
-        <v>75695</v>
+        <v>80000</v>
       </c>
     </row>
     <row r="123">
@@ -5218,7 +5236,15 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>SPR</t>
+          <t>GCL</t>
+        </is>
+      </c>
+      <c r="C123">
+        <v>10695</v>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>manual transport count</t>
         </is>
       </c>
       <c r="J123">
@@ -5236,11 +5262,11 @@
     </row>
     <row r="124">
       <c r="A124">
-        <v>1927</v>
+        <v>1926</v>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>GCL</t>
+          <t>SPR</t>
         </is>
       </c>
       <c r="J124">
@@ -5250,10 +5276,10 @@
         <v>2002000</v>
       </c>
       <c r="M124">
-        <v>91069</v>
+        <v>45412</v>
       </c>
       <c r="N124">
-        <v>70000</v>
+        <v>75695</v>
       </c>
     </row>
     <row r="125">
@@ -5262,7 +5288,7 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>SPR</t>
+          <t>GCL</t>
         </is>
       </c>
       <c r="J125">
@@ -5280,11 +5306,11 @@
     </row>
     <row r="126">
       <c r="A126">
-        <v>1928</v>
+        <v>1927</v>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>GCL</t>
+          <t>SPR</t>
         </is>
       </c>
       <c r="J126">
@@ -5294,7 +5320,7 @@
         <v>2002000</v>
       </c>
       <c r="M126">
-        <v>38000</v>
+        <v>91069</v>
       </c>
       <c r="N126">
         <v>70000</v>
@@ -5306,7 +5332,7 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>SPR</t>
+          <t>GCL</t>
         </is>
       </c>
       <c r="J127">
@@ -5324,32 +5350,24 @@
     </row>
     <row r="128">
       <c r="A128">
-        <v>1929</v>
+        <v>1928</v>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>GCL</t>
-        </is>
-      </c>
-      <c r="C128">
-        <v>3018</v>
-      </c>
-      <c r="F128" t="inlineStr">
-        <is>
-          <t>fishery officer</t>
+          <t>SPR</t>
         </is>
       </c>
       <c r="J128">
         <v>0</v>
       </c>
       <c r="L128">
-        <v>1505000</v>
+        <v>2002000</v>
       </c>
       <c r="M128">
-        <v>18000</v>
+        <v>38000</v>
       </c>
       <c r="N128">
-        <v>138018</v>
+        <v>70000</v>
       </c>
     </row>
     <row r="129">
@@ -5358,14 +5376,22 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>SPR</t>
+          <t>GCL</t>
+        </is>
+      </c>
+      <c r="C129">
+        <v>3018</v>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>fishery officer</t>
         </is>
       </c>
       <c r="J129">
         <v>0</v>
       </c>
       <c r="L129">
-        <v>2002000</v>
+        <v>1505000</v>
       </c>
       <c r="M129">
         <v>18000</v>
@@ -5376,32 +5402,24 @@
     </row>
     <row r="130">
       <c r="A130">
-        <v>1930</v>
+        <v>1929</v>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>GCL</t>
-        </is>
-      </c>
-      <c r="C130">
-        <v>9501</v>
-      </c>
-      <c r="F130" t="inlineStr">
-        <is>
-          <t>fishery officer</t>
+          <t>SPR</t>
         </is>
       </c>
       <c r="J130">
         <v>0</v>
       </c>
       <c r="L130">
-        <v>0</v>
+        <v>2002000</v>
       </c>
       <c r="M130">
-        <v>58600</v>
+        <v>18000</v>
       </c>
       <c r="N130">
-        <v>49501</v>
+        <v>138018</v>
       </c>
     </row>
     <row r="131">
@@ -5410,17 +5428,15 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>SPR</t>
-        </is>
-      </c>
-      <c r="D131" t="inlineStr">
-        <is>
-          <t>heavy</t>
-        </is>
+          <t>GCL</t>
+        </is>
+      </c>
+      <c r="C131">
+        <v>9501</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>partial shoreline estimate</t>
+          <t>fishery officer</t>
         </is>
       </c>
       <c r="J131">
@@ -5438,19 +5454,21 @@
     </row>
     <row r="132">
       <c r="A132">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>GCL</t>
-        </is>
-      </c>
-      <c r="C132">
-        <v>6920</v>
+          <t>SPR</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>heavy</t>
+        </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>fishery officer</t>
+          <t>partial shoreline estimate</t>
         </is>
       </c>
       <c r="J132">
@@ -5460,10 +5478,10 @@
         <v>0</v>
       </c>
       <c r="M132">
-        <v>59260</v>
+        <v>58600</v>
       </c>
       <c r="N132">
-        <v>56920</v>
+        <v>49501</v>
       </c>
     </row>
     <row r="133">
@@ -5472,17 +5490,15 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>SPR</t>
-        </is>
-      </c>
-      <c r="D133" t="inlineStr">
-        <is>
-          <t>heavy</t>
-        </is>
+          <t>GCL</t>
+        </is>
+      </c>
+      <c r="C133">
+        <v>6920</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>partial shoreline estimate</t>
+          <t>fishery officer</t>
         </is>
       </c>
       <c r="J133">
@@ -5500,32 +5516,34 @@
     </row>
     <row r="134">
       <c r="A134">
-        <v>1932</v>
+        <v>1931</v>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>GCL</t>
-        </is>
-      </c>
-      <c r="C134">
-        <v>2472</v>
+          <t>SPR</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>heavy</t>
+        </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>fishery officer</t>
+          <t>partial shoreline estimate</t>
         </is>
       </c>
       <c r="J134">
         <v>0</v>
       </c>
       <c r="L134">
-        <v>2002000</v>
+        <v>0</v>
       </c>
       <c r="M134">
-        <v>105000</v>
+        <v>59260</v>
       </c>
       <c r="N134">
-        <v>37472</v>
+        <v>56920</v>
       </c>
     </row>
     <row r="135">
@@ -5534,24 +5552,22 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>SPR</t>
-        </is>
-      </c>
-      <c r="D135" t="inlineStr">
-        <is>
-          <t>heavy</t>
-        </is>
+          <t>GCL</t>
+        </is>
+      </c>
+      <c r="C135">
+        <v>2472</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>partial shoreline estimate</t>
+          <t>fishery officer</t>
         </is>
       </c>
       <c r="J135">
         <v>0</v>
       </c>
       <c r="L135">
-        <v>1505000</v>
+        <v>2002000</v>
       </c>
       <c r="M135">
         <v>105000</v>
@@ -5562,32 +5578,34 @@
     </row>
     <row r="136">
       <c r="A136">
-        <v>1933</v>
+        <v>1932</v>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>GCL</t>
-        </is>
-      </c>
-      <c r="C136">
-        <v>1706</v>
+          <t>SPR</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>heavy</t>
+        </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>fishery officer</t>
+          <t>partial shoreline estimate</t>
         </is>
       </c>
       <c r="J136">
         <v>0</v>
       </c>
       <c r="L136">
-        <v>0</v>
+        <v>1505000</v>
       </c>
       <c r="M136">
-        <v>80500</v>
+        <v>105000</v>
       </c>
       <c r="N136">
-        <v>9206</v>
+        <v>37472</v>
       </c>
     </row>
     <row r="137">
@@ -5596,24 +5614,22 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>SPR</t>
-        </is>
-      </c>
-      <c r="D137" t="inlineStr">
-        <is>
-          <t>heavy</t>
-        </is>
+          <t>GCL</t>
+        </is>
+      </c>
+      <c r="C137">
+        <v>1706</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>partial shoreline estimate</t>
+          <t>fishery officer</t>
         </is>
       </c>
       <c r="J137">
         <v>0</v>
       </c>
       <c r="L137">
-        <v>2002000</v>
+        <v>0</v>
       </c>
       <c r="M137">
         <v>80500</v>
@@ -5624,32 +5640,34 @@
     </row>
     <row r="138">
       <c r="A138">
-        <v>1934</v>
+        <v>1933</v>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>GCL</t>
-        </is>
-      </c>
-      <c r="C138">
-        <v>4858</v>
+          <t>SPR</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>heavy</t>
+        </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>fishery officer</t>
+          <t>partial shoreline estimate</t>
         </is>
       </c>
       <c r="J138">
         <v>0</v>
       </c>
       <c r="L138">
-        <v>0</v>
+        <v>2002000</v>
       </c>
       <c r="M138">
-        <v>81500</v>
+        <v>80500</v>
       </c>
       <c r="N138">
-        <v>19858</v>
+        <v>9206</v>
       </c>
     </row>
     <row r="139">
@@ -5658,17 +5676,15 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>SPR</t>
-        </is>
-      </c>
-      <c r="D139" t="inlineStr">
-        <is>
-          <t>heavy</t>
-        </is>
+          <t>GCL</t>
+        </is>
+      </c>
+      <c r="C139">
+        <v>4858</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>partial shoreline estimate</t>
+          <t>fishery officer</t>
         </is>
       </c>
       <c r="J139">
@@ -5686,19 +5702,21 @@
     </row>
     <row r="140">
       <c r="A140">
-        <v>1935</v>
+        <v>1934</v>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>GCL</t>
-        </is>
-      </c>
-      <c r="C140">
-        <v>5953</v>
+          <t>SPR</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>heavy</t>
+        </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>fishery officer</t>
+          <t>partial shoreline estimate</t>
         </is>
       </c>
       <c r="J140">
@@ -5708,10 +5726,10 @@
         <v>0</v>
       </c>
       <c r="M140">
-        <v>71020</v>
+        <v>81500</v>
       </c>
       <c r="N140">
-        <v>50953</v>
+        <v>19858</v>
       </c>
     </row>
     <row r="141">
@@ -5720,17 +5738,15 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>SPR</t>
-        </is>
-      </c>
-      <c r="D141" t="inlineStr">
-        <is>
-          <t>heavy</t>
-        </is>
+          <t>GCL</t>
+        </is>
+      </c>
+      <c r="C141">
+        <v>5953</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>partial shoreline estimate</t>
+          <t>fishery officer</t>
         </is>
       </c>
       <c r="J141">
@@ -5748,19 +5764,21 @@
     </row>
     <row r="142">
       <c r="A142">
-        <v>1936</v>
+        <v>1935</v>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>GCL</t>
-        </is>
-      </c>
-      <c r="C142">
-        <v>12206</v>
+          <t>SPR</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>heavy</t>
+        </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>fishery officer</t>
+          <t>partial shoreline estimate</t>
         </is>
       </c>
       <c r="J142">
@@ -5770,10 +5788,10 @@
         <v>0</v>
       </c>
       <c r="M142">
-        <v>94580</v>
+        <v>71020</v>
       </c>
       <c r="N142">
-        <v>14206</v>
+        <v>50953</v>
       </c>
     </row>
     <row r="143">
@@ -5782,17 +5800,15 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>SPR</t>
-        </is>
-      </c>
-      <c r="D143" t="inlineStr">
-        <is>
-          <t>heavy</t>
-        </is>
+          <t>GCL</t>
+        </is>
+      </c>
+      <c r="C143">
+        <v>12206</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>partial shoreline estimate</t>
+          <t>fishery officer</t>
         </is>
       </c>
       <c r="J143">
@@ -5810,19 +5826,21 @@
     </row>
     <row r="144">
       <c r="A144">
-        <v>1937</v>
+        <v>1936</v>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>GCL</t>
-        </is>
-      </c>
-      <c r="C144">
-        <v>7365</v>
+          <t>SPR</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>heavy</t>
+        </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>fishery officer</t>
+          <t>partial shoreline estimate</t>
         </is>
       </c>
       <c r="J144">
@@ -5832,10 +5850,10 @@
         <v>0</v>
       </c>
       <c r="M144">
-        <v>61000</v>
+        <v>94580</v>
       </c>
       <c r="N144">
-        <v>45365</v>
+        <v>14206</v>
       </c>
     </row>
     <row r="145">
@@ -5844,7 +5862,15 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>SPR</t>
+          <t>GCL</t>
+        </is>
+      </c>
+      <c r="C145">
+        <v>7365</v>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>fishery officer</t>
         </is>
       </c>
       <c r="J145">
@@ -5862,19 +5888,11 @@
     </row>
     <row r="146">
       <c r="A146">
-        <v>1938</v>
+        <v>1937</v>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>GCL</t>
-        </is>
-      </c>
-      <c r="C146">
-        <v>5894</v>
-      </c>
-      <c r="F146" t="inlineStr">
-        <is>
-          <t>fishery officer</t>
+          <t>SPR</t>
         </is>
       </c>
       <c r="J146">
@@ -5884,10 +5902,10 @@
         <v>0</v>
       </c>
       <c r="M146">
-        <v>47300</v>
+        <v>61000</v>
       </c>
       <c r="N146">
-        <v>15894</v>
+        <v>45365</v>
       </c>
     </row>
     <row r="147">
@@ -5896,17 +5914,15 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>SPR</t>
-        </is>
-      </c>
-      <c r="D147" t="inlineStr">
-        <is>
-          <t>heavy</t>
-        </is>
+          <t>GCL</t>
+        </is>
+      </c>
+      <c r="C147">
+        <v>5894</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>partial shoreline estimate</t>
+          <t>fishery officer</t>
         </is>
       </c>
       <c r="J147">
@@ -5924,19 +5940,21 @@
     </row>
     <row r="148">
       <c r="A148">
-        <v>1939</v>
+        <v>1938</v>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>GCL</t>
-        </is>
-      </c>
-      <c r="C148">
-        <v>3119</v>
+          <t>SPR</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>heavy</t>
+        </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>fishery officer</t>
+          <t>partial shoreline estimate</t>
         </is>
       </c>
       <c r="J148">
@@ -5946,10 +5964,10 @@
         <v>0</v>
       </c>
       <c r="M148">
-        <v>51000</v>
+        <v>47300</v>
       </c>
       <c r="N148">
-        <v>17119</v>
+        <v>15894</v>
       </c>
     </row>
     <row r="149">
@@ -5958,17 +5976,15 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>SPR</t>
-        </is>
-      </c>
-      <c r="D149" t="inlineStr">
-        <is>
-          <t>heavy</t>
-        </is>
+          <t>GCL</t>
+        </is>
+      </c>
+      <c r="C149">
+        <v>3119</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>partial shoreline estimate</t>
+          <t>fishery officer</t>
         </is>
       </c>
       <c r="J149">
@@ -5986,19 +6002,21 @@
     </row>
     <row r="150">
       <c r="A150">
-        <v>1940</v>
+        <v>1939</v>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>GCL</t>
-        </is>
-      </c>
-      <c r="C150">
-        <v>2936</v>
+          <t>SPR</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>heavy</t>
+        </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>fishery officer</t>
+          <t>partial shoreline estimate</t>
         </is>
       </c>
       <c r="J150">
@@ -6008,10 +6026,10 @@
         <v>0</v>
       </c>
       <c r="M150">
-        <v>26580</v>
+        <v>51000</v>
       </c>
       <c r="N150">
-        <v>62936</v>
+        <v>17119</v>
       </c>
     </row>
     <row r="151">
@@ -6020,17 +6038,15 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>SPR</t>
-        </is>
-      </c>
-      <c r="D151" t="inlineStr">
-        <is>
-          <t>heavy</t>
-        </is>
+          <t>GCL</t>
+        </is>
+      </c>
+      <c r="C151">
+        <v>2936</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>partial shoreline estimate</t>
+          <t>fishery officer</t>
         </is>
       </c>
       <c r="J151">
@@ -6048,19 +6064,21 @@
     </row>
     <row r="152">
       <c r="A152">
-        <v>1941</v>
+        <v>1940</v>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>GCL</t>
-        </is>
-      </c>
-      <c r="C152">
-        <v>14625</v>
+          <t>SPR</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>heavy</t>
+        </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>fishery officer</t>
+          <t>partial shoreline estimate</t>
         </is>
       </c>
       <c r="J152">
@@ -6070,10 +6088,10 @@
         <v>0</v>
       </c>
       <c r="M152">
-        <v>25000</v>
+        <v>26580</v>
       </c>
       <c r="N152">
-        <v>16625</v>
+        <v>62936</v>
       </c>
     </row>
     <row r="153">
@@ -6082,17 +6100,15 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>SPR</t>
-        </is>
-      </c>
-      <c r="D153" t="inlineStr">
-        <is>
-          <t>medium</t>
-        </is>
+          <t>GCL</t>
+        </is>
+      </c>
+      <c r="C153">
+        <v>14625</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>partial shoreline estimate</t>
+          <t>fishery officer</t>
         </is>
       </c>
       <c r="J153">
@@ -6110,19 +6126,21 @@
     </row>
     <row r="154">
       <c r="A154">
-        <v>1942</v>
+        <v>1941</v>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>GCL</t>
-        </is>
-      </c>
-      <c r="C154">
-        <v>15823</v>
+          <t>SPR</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>fishery officer</t>
+          <t>partial shoreline estimate</t>
         </is>
       </c>
       <c r="J154">
@@ -6132,10 +6150,10 @@
         <v>0</v>
       </c>
       <c r="M154">
-        <v>29200</v>
+        <v>25000</v>
       </c>
       <c r="N154">
-        <v>22823</v>
+        <v>16625</v>
       </c>
     </row>
     <row r="155">
@@ -6144,17 +6162,15 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>SPR</t>
-        </is>
-      </c>
-      <c r="D155" t="inlineStr">
-        <is>
-          <t>heavy</t>
-        </is>
+          <t>GCL</t>
+        </is>
+      </c>
+      <c r="C155">
+        <v>15823</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>partial shoreline estimate</t>
+          <t>fishery officer</t>
         </is>
       </c>
       <c r="J155">
@@ -6172,19 +6188,21 @@
     </row>
     <row r="156">
       <c r="A156">
-        <v>1943</v>
+        <v>1942</v>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>GCL</t>
-        </is>
-      </c>
-      <c r="C156">
-        <v>5421</v>
+          <t>SPR</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>heavy</t>
+        </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>fishery officer</t>
+          <t>partial shoreline estimate</t>
         </is>
       </c>
       <c r="J156">
@@ -6194,10 +6212,10 @@
         <v>0</v>
       </c>
       <c r="M156">
-        <v>38860</v>
+        <v>29200</v>
       </c>
       <c r="N156">
-        <v>10421</v>
+        <v>22823</v>
       </c>
     </row>
     <row r="157">
@@ -6206,7 +6224,15 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>SPR</t>
+          <t>GCL</t>
+        </is>
+      </c>
+      <c r="C157">
+        <v>5421</v>
+      </c>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>fishery officer</t>
         </is>
       </c>
       <c r="J157">
@@ -6224,19 +6250,11 @@
     </row>
     <row r="158">
       <c r="A158">
-        <v>1944</v>
+        <v>1943</v>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>GCL</t>
-        </is>
-      </c>
-      <c r="C158">
-        <v>4537</v>
-      </c>
-      <c r="F158" t="inlineStr">
-        <is>
-          <t>fishery officer</t>
+          <t>SPR</t>
         </is>
       </c>
       <c r="J158">
@@ -6246,10 +6264,10 @@
         <v>0</v>
       </c>
       <c r="M158">
-        <v>14600</v>
+        <v>38860</v>
       </c>
       <c r="N158">
-        <v>9537</v>
+        <v>10421</v>
       </c>
     </row>
     <row r="159">
@@ -6258,7 +6276,15 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>SPR</t>
+          <t>GCL</t>
+        </is>
+      </c>
+      <c r="C159">
+        <v>4537</v>
+      </c>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>fishery officer</t>
         </is>
       </c>
       <c r="J159">
@@ -6276,19 +6302,11 @@
     </row>
     <row r="160">
       <c r="A160">
-        <v>1945</v>
+        <v>1944</v>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>GCL</t>
-        </is>
-      </c>
-      <c r="C160">
-        <v>26245</v>
-      </c>
-      <c r="F160" t="inlineStr">
-        <is>
-          <t>fishery officer</t>
+          <t>SPR</t>
         </is>
       </c>
       <c r="J160">
@@ -6298,10 +6316,10 @@
         <v>0</v>
       </c>
       <c r="M160">
-        <v>11800</v>
+        <v>14600</v>
       </c>
       <c r="N160">
-        <v>40245</v>
+        <v>9537</v>
       </c>
     </row>
     <row r="161">
@@ -6310,7 +6328,15 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>SPR</t>
+          <t>GCL</t>
+        </is>
+      </c>
+      <c r="C161">
+        <v>26245</v>
+      </c>
+      <c r="F161" t="inlineStr">
+        <is>
+          <t>fishery officer</t>
         </is>
       </c>
       <c r="J161">
@@ -6328,19 +6354,11 @@
     </row>
     <row r="162">
       <c r="A162">
-        <v>1946</v>
+        <v>1945</v>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>GCL</t>
-        </is>
-      </c>
-      <c r="C162">
-        <v>5986</v>
-      </c>
-      <c r="F162" t="inlineStr">
-        <is>
-          <t>fishery officer</t>
+          <t>SPR</t>
         </is>
       </c>
       <c r="J162">
@@ -6350,10 +6368,10 @@
         <v>0</v>
       </c>
       <c r="M162">
-        <v>13980</v>
+        <v>11800</v>
       </c>
       <c r="N162">
-        <v>19986</v>
+        <v>40245</v>
       </c>
     </row>
     <row r="163">
@@ -6362,7 +6380,15 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>SPR</t>
+          <t>GCL</t>
+        </is>
+      </c>
+      <c r="C163">
+        <v>5986</v>
+      </c>
+      <c r="F163" t="inlineStr">
+        <is>
+          <t>fishery officer</t>
         </is>
       </c>
       <c r="J163">
@@ -6380,19 +6406,11 @@
     </row>
     <row r="164">
       <c r="A164">
-        <v>1947</v>
+        <v>1946</v>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>GCL</t>
-        </is>
-      </c>
-      <c r="C164">
-        <v>5900</v>
-      </c>
-      <c r="F164" t="inlineStr">
-        <is>
-          <t>fishery officer</t>
+          <t>SPR</t>
         </is>
       </c>
       <c r="J164">
@@ -6402,10 +6420,10 @@
         <v>0</v>
       </c>
       <c r="M164">
-        <v>5440</v>
+        <v>13980</v>
       </c>
       <c r="N164">
-        <v>12900</v>
+        <v>19986</v>
       </c>
     </row>
     <row r="165">
@@ -6414,7 +6432,15 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>SPR</t>
+          <t>GCL</t>
+        </is>
+      </c>
+      <c r="C165">
+        <v>5900</v>
+      </c>
+      <c r="F165" t="inlineStr">
+        <is>
+          <t>fishery officer</t>
         </is>
       </c>
       <c r="J165">
@@ -6432,19 +6458,11 @@
     </row>
     <row r="166">
       <c r="A166">
-        <v>1948</v>
+        <v>1947</v>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>GCL</t>
-        </is>
-      </c>
-      <c r="C166">
-        <v>4167</v>
-      </c>
-      <c r="F166" t="inlineStr">
-        <is>
-          <t>fishery officer</t>
+          <t>SPR</t>
         </is>
       </c>
       <c r="J166">
@@ -6454,10 +6472,10 @@
         <v>0</v>
       </c>
       <c r="M166">
-        <v>9560</v>
+        <v>5440</v>
       </c>
       <c r="N166">
-        <v>11167</v>
+        <v>12900</v>
       </c>
     </row>
     <row r="167">
@@ -6466,7 +6484,15 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>SPR</t>
+          <t>GCL</t>
+        </is>
+      </c>
+      <c r="C167">
+        <v>4167</v>
+      </c>
+      <c r="F167" t="inlineStr">
+        <is>
+          <t>fishery officer</t>
         </is>
       </c>
       <c r="J167">
@@ -6484,19 +6510,11 @@
     </row>
     <row r="168">
       <c r="A168">
-        <v>1949</v>
+        <v>1948</v>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>GCL</t>
-        </is>
-      </c>
-      <c r="C168">
-        <v>50418</v>
-      </c>
-      <c r="F168" t="inlineStr">
-        <is>
-          <t>fishery officer</t>
+          <t>SPR</t>
         </is>
       </c>
       <c r="J168">
@@ -6506,10 +6524,10 @@
         <v>0</v>
       </c>
       <c r="M168">
-        <v>35720</v>
+        <v>9560</v>
       </c>
       <c r="N168">
-        <v>80418</v>
+        <v>11167</v>
       </c>
     </row>
     <row r="169">
@@ -6518,7 +6536,15 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>SPR</t>
+          <t>GCL</t>
+        </is>
+      </c>
+      <c r="C169">
+        <v>50418</v>
+      </c>
+      <c r="F169" t="inlineStr">
+        <is>
+          <t>fishery officer</t>
         </is>
       </c>
       <c r="J169">
@@ -6536,19 +6562,11 @@
     </row>
     <row r="170">
       <c r="A170">
-        <v>1950</v>
+        <v>1949</v>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>GCL</t>
-        </is>
-      </c>
-      <c r="C170">
-        <v>20000</v>
-      </c>
-      <c r="F170" t="inlineStr">
-        <is>
-          <t>fishery officer</t>
+          <t>SPR</t>
         </is>
       </c>
       <c r="J170">
@@ -6558,10 +6576,10 @@
         <v>0</v>
       </c>
       <c r="M170">
-        <v>55190</v>
+        <v>35720</v>
       </c>
       <c r="N170">
-        <v>44000</v>
+        <v>80418</v>
       </c>
     </row>
     <row r="171">
@@ -6570,11 +6588,11 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>SPR</t>
+          <t>GCL</t>
         </is>
       </c>
       <c r="C171">
-        <v>10000</v>
+        <v>20000</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -6596,15 +6614,15 @@
     </row>
     <row r="172">
       <c r="A172">
-        <v>1951</v>
+        <v>1950</v>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>GCL</t>
+          <t>SPR</t>
         </is>
       </c>
       <c r="C172">
-        <v>50000</v>
+        <v>10000</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -6618,10 +6636,10 @@
         <v>0</v>
       </c>
       <c r="M172">
-        <v>76018</v>
+        <v>55190</v>
       </c>
       <c r="N172">
-        <v>89000</v>
+        <v>44000</v>
       </c>
     </row>
     <row r="173">
@@ -6630,11 +6648,11 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>SPR</t>
+          <t>GCL</t>
         </is>
       </c>
       <c r="C173">
-        <v>25000</v>
+        <v>50000</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -6656,15 +6674,15 @@
     </row>
     <row r="174">
       <c r="A174">
-        <v>1952</v>
+        <v>1951</v>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>GCL</t>
+          <t>SPR</t>
         </is>
       </c>
       <c r="C174">
-        <v>12000</v>
+        <v>25000</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -6678,10 +6696,10 @@
         <v>0</v>
       </c>
       <c r="M174">
-        <v>50094</v>
+        <v>76018</v>
       </c>
       <c r="N174">
-        <v>36000</v>
+        <v>89000</v>
       </c>
     </row>
     <row r="175">
@@ -6690,11 +6708,11 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>SPR</t>
+          <t>GCL</t>
         </is>
       </c>
       <c r="C175">
-        <v>10000</v>
+        <v>12000</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -6716,15 +6734,15 @@
     </row>
     <row r="176">
       <c r="A176">
-        <v>1953</v>
+        <v>1952</v>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>GCL</t>
+          <t>SPR</t>
         </is>
       </c>
       <c r="C176">
-        <v>30000</v>
+        <v>10000</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -6738,10 +6756,10 @@
         <v>0</v>
       </c>
       <c r="M176">
-        <v>76328</v>
+        <v>50094</v>
       </c>
       <c r="N176">
-        <v>64000</v>
+        <v>36000</v>
       </c>
     </row>
     <row r="177">
@@ -6750,11 +6768,11 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>SPR</t>
+          <t>GCL</t>
         </is>
       </c>
       <c r="C177">
-        <v>20000</v>
+        <v>30000</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -6776,11 +6794,11 @@
     </row>
     <row r="178">
       <c r="A178">
-        <v>1954</v>
+        <v>1953</v>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>GCL</t>
+          <t>SPR</t>
         </is>
       </c>
       <c r="C178">
@@ -6798,10 +6816,10 @@
         <v>0</v>
       </c>
       <c r="M178">
-        <v>38405</v>
+        <v>76328</v>
       </c>
       <c r="N178">
-        <v>65000</v>
+        <v>64000</v>
       </c>
     </row>
     <row r="179">
@@ -6810,11 +6828,11 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>SPR</t>
+          <t>GCL</t>
         </is>
       </c>
       <c r="C179">
-        <v>15000</v>
+        <v>20000</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -6836,11 +6854,11 @@
     </row>
     <row r="180">
       <c r="A180">
-        <v>1955</v>
+        <v>1954</v>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>GCL</t>
+          <t>SPR</t>
         </is>
       </c>
       <c r="C180">
@@ -6858,10 +6876,10 @@
         <v>0</v>
       </c>
       <c r="M180">
-        <v>28714</v>
+        <v>38405</v>
       </c>
       <c r="N180">
-        <v>39000</v>
+        <v>65000</v>
       </c>
     </row>
     <row r="181">
@@ -6870,11 +6888,11 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>SPR</t>
+          <t>GCL</t>
         </is>
       </c>
       <c r="C181">
-        <v>10000</v>
+        <v>15000</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -6896,15 +6914,15 @@
     </row>
     <row r="182">
       <c r="A182">
-        <v>1956</v>
+        <v>1955</v>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>GCL</t>
+          <t>SPR</t>
         </is>
       </c>
       <c r="C182">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -6918,10 +6936,10 @@
         <v>0</v>
       </c>
       <c r="M182">
-        <v>8934</v>
+        <v>28714</v>
       </c>
       <c r="N182">
-        <v>17000</v>
+        <v>39000</v>
       </c>
     </row>
     <row r="183">
@@ -6930,7 +6948,7 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>SPR</t>
+          <t>GCL</t>
         </is>
       </c>
       <c r="C183">
@@ -6956,15 +6974,15 @@
     </row>
     <row r="184">
       <c r="A184">
-        <v>1957</v>
+        <v>1956</v>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>GCL</t>
+          <t>SPR</t>
         </is>
       </c>
       <c r="C184">
-        <v>100000</v>
+        <v>5000</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -6978,10 +6996,10 @@
         <v>0</v>
       </c>
       <c r="M184">
-        <v>11749</v>
+        <v>8934</v>
       </c>
       <c r="N184">
-        <v>147000</v>
+        <v>17000</v>
       </c>
     </row>
     <row r="185">
@@ -6990,11 +7008,11 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>SPR</t>
+          <t>GCL</t>
         </is>
       </c>
       <c r="C185">
-        <v>40000</v>
+        <v>100000</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -7016,15 +7034,15 @@
     </row>
     <row r="186">
       <c r="A186">
-        <v>1958</v>
+        <v>1957</v>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>GCL</t>
+          <t>SPR</t>
         </is>
       </c>
       <c r="C186">
-        <v>20000</v>
+        <v>40000</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -7038,10 +7056,10 @@
         <v>0</v>
       </c>
       <c r="M186">
-        <v>8296</v>
+        <v>11749</v>
       </c>
       <c r="N186">
-        <v>54000</v>
+        <v>147000</v>
       </c>
     </row>
     <row r="187">
@@ -7050,7 +7068,7 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>SPR</t>
+          <t>GCL</t>
         </is>
       </c>
       <c r="C187">
@@ -7076,11 +7094,11 @@
     </row>
     <row r="188">
       <c r="A188">
-        <v>1959</v>
+        <v>1958</v>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>GCL</t>
+          <t>SPR</t>
         </is>
       </c>
       <c r="C188">
@@ -7098,7 +7116,7 @@
         <v>0</v>
       </c>
       <c r="M188">
-        <v>6966</v>
+        <v>8296</v>
       </c>
       <c r="N188">
         <v>54000</v>
@@ -7110,7 +7128,7 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>SPR</t>
+          <t>GCL</t>
         </is>
       </c>
       <c r="C189">
@@ -7136,11 +7154,11 @@
     </row>
     <row r="190">
       <c r="A190">
-        <v>1960</v>
+        <v>1959</v>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>GCL</t>
+          <t>SPR</t>
         </is>
       </c>
       <c r="C190">
@@ -7158,10 +7176,10 @@
         <v>0</v>
       </c>
       <c r="M190">
-        <v>9144</v>
+        <v>6966</v>
       </c>
       <c r="N190">
-        <v>50000</v>
+        <v>54000</v>
       </c>
     </row>
     <row r="191">
@@ -7170,7 +7188,7 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>SPR</t>
+          <t>GCL</t>
         </is>
       </c>
       <c r="C191">
@@ -7196,15 +7214,15 @@
     </row>
     <row r="192">
       <c r="A192">
-        <v>1961</v>
+        <v>1960</v>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>GCL</t>
+          <t>SPR</t>
         </is>
       </c>
       <c r="C192">
-        <v>18000</v>
+        <v>20000</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -7218,7 +7236,7 @@
         <v>0</v>
       </c>
       <c r="M192">
-        <v>21864</v>
+        <v>9144</v>
       </c>
       <c r="N192">
         <v>50000</v>
@@ -7230,7 +7248,7 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>SPR</t>
+          <t>GCL</t>
         </is>
       </c>
       <c r="C193">
@@ -7256,15 +7274,15 @@
     </row>
     <row r="194">
       <c r="A194">
-        <v>1962</v>
+        <v>1961</v>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>GCL</t>
+          <t>SPR</t>
         </is>
       </c>
       <c r="C194">
-        <v>13000</v>
+        <v>18000</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -7278,10 +7296,10 @@
         <v>0</v>
       </c>
       <c r="M194">
-        <v>16299</v>
+        <v>21864</v>
       </c>
       <c r="N194">
-        <v>58000</v>
+        <v>50000</v>
       </c>
     </row>
     <row r="195">
@@ -7290,11 +7308,11 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>SPR</t>
+          <t>GCL</t>
         </is>
       </c>
       <c r="C195">
-        <v>15000</v>
+        <v>13000</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -7316,15 +7334,15 @@
     </row>
     <row r="196">
       <c r="A196">
-        <v>1963</v>
+        <v>1962</v>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>GCL</t>
+          <t>SPR</t>
         </is>
       </c>
       <c r="C196">
-        <v>6000</v>
+        <v>15000</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -7338,10 +7356,10 @@
         <v>0</v>
       </c>
       <c r="M196">
-        <v>11065</v>
+        <v>16299</v>
       </c>
       <c r="N196">
-        <v>50000</v>
+        <v>58000</v>
       </c>
     </row>
     <row r="197">
@@ -7350,11 +7368,11 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>SPR</t>
+          <t>GCL</t>
         </is>
       </c>
       <c r="C197">
-        <v>26000</v>
+        <v>6000</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -7376,15 +7394,15 @@
     </row>
     <row r="198">
       <c r="A198">
-        <v>1964</v>
+        <v>1963</v>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>GCL</t>
+          <t>SPR</t>
         </is>
       </c>
       <c r="C198">
-        <v>70000</v>
+        <v>26000</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -7398,10 +7416,10 @@
         <v>0</v>
       </c>
       <c r="M198">
-        <v>11218</v>
+        <v>11065</v>
       </c>
       <c r="N198">
-        <v>113000</v>
+        <v>50000</v>
       </c>
     </row>
     <row r="199">
@@ -7410,11 +7428,11 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>SPR</t>
+          <t>GCL</t>
         </is>
       </c>
       <c r="C199">
-        <v>13000</v>
+        <v>70000</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -7436,15 +7454,15 @@
     </row>
     <row r="200">
       <c r="A200">
-        <v>1965</v>
+        <v>1964</v>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>GCL</t>
+          <t>SPR</t>
         </is>
       </c>
       <c r="C200">
-        <v>23000</v>
+        <v>13000</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -7458,10 +7476,10 @@
         <v>0</v>
       </c>
       <c r="M200">
-        <v>17657</v>
+        <v>11218</v>
       </c>
       <c r="N200">
-        <v>56000</v>
+        <v>113000</v>
       </c>
     </row>
     <row r="201">
@@ -7470,11 +7488,11 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>SPR</t>
+          <t>GCL</t>
         </is>
       </c>
       <c r="C201">
-        <v>15000</v>
+        <v>23000</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -7496,15 +7514,15 @@
     </row>
     <row r="202">
       <c r="A202">
-        <v>1966</v>
+        <v>1965</v>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>GCL</t>
+          <t>SPR</t>
         </is>
       </c>
       <c r="C202">
-        <v>68000</v>
+        <v>15000</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -7518,10 +7536,10 @@
         <v>0</v>
       </c>
       <c r="M202">
-        <v>29151</v>
+        <v>17657</v>
       </c>
       <c r="N202">
-        <v>176000</v>
+        <v>56000</v>
       </c>
     </row>
     <row r="203">
@@ -7530,11 +7548,11 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>SPR</t>
+          <t>GCL</t>
         </is>
       </c>
       <c r="C203">
-        <v>28000</v>
+        <v>68000</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -7556,15 +7574,15 @@
     </row>
     <row r="204">
       <c r="A204">
-        <v>1967</v>
+        <v>1966</v>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>GCL</t>
+          <t>SPR</t>
         </is>
       </c>
       <c r="C204">
-        <v>33500</v>
+        <v>28000</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -7578,10 +7596,10 @@
         <v>0</v>
       </c>
       <c r="M204">
-        <v>31022</v>
+        <v>29151</v>
       </c>
       <c r="N204">
-        <v>135500</v>
+        <v>176000</v>
       </c>
     </row>
     <row r="205">
@@ -7590,11 +7608,11 @@
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>SPR</t>
+          <t>GCL</t>
         </is>
       </c>
       <c r="C205">
-        <v>22000</v>
+        <v>33500</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -7616,15 +7634,15 @@
     </row>
     <row r="206">
       <c r="A206">
-        <v>1968</v>
+        <v>1967</v>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>GCL</t>
+          <t>SPR</t>
         </is>
       </c>
       <c r="C206">
-        <v>78600</v>
+        <v>22000</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -7638,10 +7656,10 @@
         <v>0</v>
       </c>
       <c r="M206">
-        <v>28828</v>
+        <v>31022</v>
       </c>
       <c r="N206">
-        <v>137600</v>
+        <v>135500</v>
       </c>
     </row>
     <row r="207">
@@ -7650,11 +7668,11 @@
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>SPR</t>
+          <t>GCL</t>
         </is>
       </c>
       <c r="C207">
-        <v>29000</v>
+        <v>78600</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -7676,15 +7694,15 @@
     </row>
     <row r="208">
       <c r="A208">
-        <v>1969</v>
+        <v>1968</v>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>GCL</t>
+          <t>SPR</t>
         </is>
       </c>
       <c r="C208">
-        <v>72900</v>
+        <v>29000</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -7698,10 +7716,10 @@
         <v>0</v>
       </c>
       <c r="M208">
-        <v>56787</v>
+        <v>28828</v>
       </c>
       <c r="N208">
-        <v>114900</v>
+        <v>137600</v>
       </c>
     </row>
     <row r="209">
@@ -7710,11 +7728,11 @@
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>SPR</t>
+          <t>GCL</t>
         </is>
       </c>
       <c r="C209">
-        <v>24000</v>
+        <v>72900</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -7736,45 +7754,32 @@
     </row>
     <row r="210">
       <c r="A210">
-        <v>1970</v>
+        <v>1969</v>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>GCL</t>
+          <t>SPR</t>
         </is>
       </c>
       <c r="C210">
-        <v>15100</v>
-      </c>
-      <c r="E210">
-        <v>14582</v>
+        <v>24000</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
           <t>fishery officer</t>
         </is>
       </c>
-      <c r="G210" t="inlineStr">
-        <is>
-          <t>commercial catch records</t>
-        </is>
-      </c>
-      <c r="H210" t="inlineStr">
-        <is>
-          <t>assumed run timing</t>
-        </is>
-      </c>
       <c r="J210">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L210">
         <v>0</v>
       </c>
       <c r="M210">
-        <v>89092</v>
+        <v>56787</v>
       </c>
       <c r="N210">
-        <v>42100</v>
+        <v>114900</v>
       </c>
     </row>
     <row r="211">
@@ -7783,14 +7788,14 @@
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>SPR</t>
+          <t>GCL</t>
         </is>
       </c>
       <c r="C211">
-        <v>18000</v>
+        <v>15100</v>
       </c>
       <c r="E211">
-        <v>23692</v>
+        <v>14582</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -7808,7 +7813,7 @@
         </is>
       </c>
       <c r="J211">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L211">
         <v>0</v>
@@ -7822,18 +7827,18 @@
     </row>
     <row r="212">
       <c r="A212">
-        <v>1971</v>
+        <v>1970</v>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>GCL</t>
+          <t>SPR</t>
         </is>
       </c>
       <c r="C212">
-        <v>39200</v>
+        <v>18000</v>
       </c>
       <c r="E212">
-        <v>13610</v>
+        <v>23692</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -7851,16 +7856,16 @@
         </is>
       </c>
       <c r="J212">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L212">
         <v>0</v>
       </c>
       <c r="M212">
-        <v>51875</v>
+        <v>89092</v>
       </c>
       <c r="N212">
-        <v>71700</v>
+        <v>42100</v>
       </c>
     </row>
     <row r="213">
@@ -7869,14 +7874,14 @@
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>SPR</t>
+          <t>GCL</t>
         </is>
       </c>
       <c r="C213">
-        <v>25000</v>
+        <v>39200</v>
       </c>
       <c r="E213">
-        <v>8665</v>
+        <v>13610</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -7894,7 +7899,7 @@
         </is>
       </c>
       <c r="J213">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L213">
         <v>0</v>
@@ -7908,18 +7913,18 @@
     </row>
     <row r="214">
       <c r="A214">
-        <v>1972</v>
+        <v>1971</v>
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>GCL</t>
+          <t>SPR</t>
         </is>
       </c>
       <c r="C214">
-        <v>93300</v>
+        <v>25000</v>
       </c>
       <c r="E214">
-        <v>83723</v>
+        <v>8665</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -7937,16 +7942,16 @@
         </is>
       </c>
       <c r="J214">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L214">
         <v>0</v>
       </c>
       <c r="M214">
-        <v>225718</v>
+        <v>51875</v>
       </c>
       <c r="N214">
-        <v>139400</v>
+        <v>71700</v>
       </c>
     </row>
     <row r="215">
@@ -7955,14 +7960,14 @@
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>SPR</t>
+          <t>GCL</t>
         </is>
       </c>
       <c r="C215">
-        <v>42600</v>
+        <v>93300</v>
       </c>
       <c r="E215">
-        <v>28930</v>
+        <v>83723</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -7980,7 +7985,7 @@
         </is>
       </c>
       <c r="J215">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L215">
         <v>0</v>
@@ -7994,18 +7999,18 @@
     </row>
     <row r="216">
       <c r="A216">
-        <v>1973</v>
+        <v>1972</v>
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>GCL</t>
+          <t>SPR</t>
         </is>
       </c>
       <c r="C216">
-        <v>216100</v>
+        <v>42600</v>
       </c>
       <c r="E216">
-        <v>165390</v>
+        <v>28930</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -8023,16 +8028,16 @@
         </is>
       </c>
       <c r="J216">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L216">
         <v>0</v>
       </c>
       <c r="M216">
-        <v>451615</v>
+        <v>225718</v>
       </c>
       <c r="N216">
-        <v>301700</v>
+        <v>139400</v>
       </c>
     </row>
     <row r="217">
@@ -8041,14 +8046,14 @@
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>SPR</t>
+          <t>GCL</t>
         </is>
       </c>
       <c r="C217">
-        <v>45600</v>
+        <v>216100</v>
       </c>
       <c r="E217">
-        <v>39337</v>
+        <v>165390</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -8066,7 +8071,7 @@
         </is>
       </c>
       <c r="J217">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L217">
         <v>0</v>
@@ -8080,18 +8085,18 @@
     </row>
     <row r="218">
       <c r="A218">
-        <v>1974</v>
+        <v>1973</v>
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>GCL</t>
+          <t>SPR</t>
         </is>
       </c>
       <c r="C218">
-        <v>56300</v>
+        <v>45600</v>
       </c>
       <c r="E218">
-        <v>109793</v>
+        <v>39337</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -8115,10 +8120,10 @@
         <v>0</v>
       </c>
       <c r="M218">
-        <v>427790</v>
+        <v>451615</v>
       </c>
       <c r="N218">
-        <v>98100</v>
+        <v>301700</v>
       </c>
     </row>
     <row r="219">
@@ -8127,14 +8132,14 @@
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>SPR</t>
+          <t>GCL</t>
         </is>
       </c>
       <c r="C219">
-        <v>35800</v>
+        <v>56300</v>
       </c>
       <c r="E219">
-        <v>91846</v>
+        <v>109793</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -8166,18 +8171,18 @@
     </row>
     <row r="220">
       <c r="A220">
-        <v>1975</v>
+        <v>1974</v>
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>GCL</t>
+          <t>SPR</t>
         </is>
       </c>
       <c r="C220">
-        <v>138100</v>
+        <v>35800</v>
       </c>
       <c r="E220">
-        <v>129499</v>
+        <v>91846</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -8201,10 +8206,10 @@
         <v>0</v>
       </c>
       <c r="M220">
-        <v>440977</v>
+        <v>427790</v>
       </c>
       <c r="N220">
-        <v>195600</v>
+        <v>98100</v>
       </c>
     </row>
     <row r="221">
@@ -8213,14 +8218,14 @@
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>SPR</t>
+          <t>GCL</t>
         </is>
       </c>
       <c r="C221">
-        <v>47500</v>
+        <v>138100</v>
       </c>
       <c r="E221">
-        <v>78617</v>
+        <v>129499</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -8252,18 +8257,18 @@
     </row>
     <row r="222">
       <c r="A222">
-        <v>1976</v>
+        <v>1975</v>
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>GCL</t>
+          <t>SPR</t>
         </is>
       </c>
       <c r="C222">
-        <v>100600</v>
+        <v>47500</v>
       </c>
       <c r="E222">
-        <v>470815</v>
+        <v>78617</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -8287,10 +8292,10 @@
         <v>0</v>
       </c>
       <c r="M222">
-        <v>1408490</v>
+        <v>440977</v>
       </c>
       <c r="N222">
-        <v>151800</v>
+        <v>195600</v>
       </c>
     </row>
     <row r="223">
@@ -8299,14 +8304,14 @@
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>SPR</t>
+          <t>GCL</t>
         </is>
       </c>
       <c r="C223">
-        <v>47700</v>
+        <v>100600</v>
       </c>
       <c r="E223">
-        <v>203610</v>
+        <v>470815</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -8338,22 +8343,22 @@
     </row>
     <row r="224">
       <c r="A224">
-        <v>1977</v>
+        <v>1976</v>
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>GCL</t>
+          <t>SPR</t>
         </is>
       </c>
       <c r="C224">
-        <v>212200</v>
+        <v>47700</v>
       </c>
       <c r="E224">
-        <v>794304.3566749521</v>
+        <v>203610</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>resistivity counter</t>
+          <t>fishery officer</t>
         </is>
       </c>
       <c r="G224" t="inlineStr">
@@ -8366,22 +8371,17 @@
           <t>assumed run timing</t>
         </is>
       </c>
-      <c r="I224" t="inlineStr">
-        <is>
-          <t>scale sampling</t>
-        </is>
-      </c>
       <c r="J224">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L224">
         <v>0</v>
       </c>
       <c r="M224">
-        <v>1122813.89493761</v>
+        <v>1408490</v>
       </c>
       <c r="N224">
-        <v>297800</v>
+        <v>151800</v>
       </c>
     </row>
     <row r="225">
@@ -8390,14 +8390,14 @@
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>SPR</t>
+          <t>GCL</t>
         </is>
       </c>
       <c r="C225">
-        <v>80800</v>
+        <v>212200</v>
       </c>
       <c r="E225">
-        <v>302449.5382626585</v>
+        <v>794304.3566749521</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -8420,7 +8420,7 @@
         </is>
       </c>
       <c r="J225">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L225">
         <v>0</v>
@@ -8434,18 +8434,18 @@
     </row>
     <row r="226">
       <c r="A226">
-        <v>1978</v>
+        <v>1977</v>
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>GCL</t>
+          <t>SPR</t>
         </is>
       </c>
       <c r="C226">
-        <v>114400</v>
+        <v>80800</v>
       </c>
       <c r="E226">
-        <v>145531.0318997159</v>
+        <v>302449.5382626585</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -8468,16 +8468,16 @@
         </is>
       </c>
       <c r="J226">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L226">
         <v>0</v>
       </c>
       <c r="M226">
-        <v>197067.6970766333</v>
+        <v>1122813.89493761</v>
       </c>
       <c r="N226">
-        <v>158900</v>
+        <v>297800</v>
       </c>
     </row>
     <row r="227">
@@ -8486,14 +8486,14 @@
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>SPR</t>
+          <t>GCL</t>
         </is>
       </c>
       <c r="C227">
-        <v>37500</v>
+        <v>114400</v>
       </c>
       <c r="E227">
-        <v>47704.66517691737</v>
+        <v>145531.0318997159</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -8516,7 +8516,7 @@
         </is>
       </c>
       <c r="J227">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L227">
         <v>0</v>
@@ -8530,18 +8530,18 @@
     </row>
     <row r="228">
       <c r="A228">
-        <v>1979</v>
+        <v>1978</v>
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>GCL</t>
+          <t>SPR</t>
         </is>
       </c>
       <c r="C228">
-        <v>263995</v>
+        <v>37500</v>
       </c>
       <c r="E228">
-        <v>540963.2816986635</v>
+        <v>47704.66517691737</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -8564,16 +8564,16 @@
         </is>
       </c>
       <c r="J228">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L228">
         <v>0</v>
       </c>
       <c r="M228">
-        <v>821100.0024423746</v>
+        <v>197067.6970766333</v>
       </c>
       <c r="N228">
-        <v>360441</v>
+        <v>158900</v>
       </c>
     </row>
     <row r="229">
@@ -8582,14 +8582,14 @@
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>SPR</t>
+          <t>GCL</t>
         </is>
       </c>
       <c r="C229">
-        <v>76446</v>
+        <v>263995</v>
       </c>
       <c r="E229">
-        <v>156648.7207437111</v>
+        <v>540963.2816986635</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -8612,7 +8612,7 @@
         </is>
       </c>
       <c r="J229">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L229">
         <v>0</v>
@@ -8626,18 +8626,18 @@
     </row>
     <row r="230">
       <c r="A230">
-        <v>1980</v>
+        <v>1979</v>
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>GCL</t>
+          <t>SPR</t>
         </is>
       </c>
       <c r="C230">
-        <v>256516</v>
+        <v>76446</v>
       </c>
       <c r="E230">
-        <v>421856.2559109447</v>
+        <v>156648.7207437111</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -8646,7 +8646,7 @@
       </c>
       <c r="G230" t="inlineStr">
         <is>
-          <t>commercial + FN catch records</t>
+          <t>commercial catch records</t>
         </is>
       </c>
       <c r="H230" t="inlineStr">
@@ -8660,16 +8660,16 @@
         </is>
       </c>
       <c r="J230">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L230">
         <v>0</v>
       </c>
       <c r="M230">
-        <v>695952.2532801195</v>
+        <v>821100.0024423746</v>
       </c>
       <c r="N230">
-        <v>415212</v>
+        <v>360441</v>
       </c>
     </row>
     <row r="231">
@@ -8678,14 +8678,14 @@
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>SPR</t>
+          <t>GCL</t>
         </is>
       </c>
       <c r="C231">
-        <v>137990</v>
+        <v>256516</v>
       </c>
       <c r="E231">
-        <v>226932.9973691749</v>
+        <v>421856.2559109447</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -8708,7 +8708,7 @@
         </is>
       </c>
       <c r="J231">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L231">
         <v>0</v>
@@ -8722,18 +8722,18 @@
     </row>
     <row r="232">
       <c r="A232">
-        <v>1981</v>
+        <v>1980</v>
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>GCL</t>
+          <t>SPR</t>
         </is>
       </c>
       <c r="C232">
-        <v>213538</v>
+        <v>137990</v>
       </c>
       <c r="E232">
-        <v>557539.3886574621</v>
+        <v>226932.9973691749</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -8756,16 +8756,16 @@
         </is>
       </c>
       <c r="J232">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L232">
         <v>0</v>
       </c>
       <c r="M232">
-        <v>1038876.317981237</v>
+        <v>695952.2532801195</v>
       </c>
       <c r="N232">
-        <v>410789</v>
+        <v>415212</v>
       </c>
     </row>
     <row r="233">
@@ -8774,14 +8774,14 @@
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>SPR</t>
+          <t>GCL</t>
         </is>
       </c>
       <c r="C233">
-        <v>139251</v>
+        <v>213538</v>
       </c>
       <c r="E233">
-        <v>363578.929323775</v>
+        <v>557539.3886574621</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -8804,7 +8804,7 @@
         </is>
       </c>
       <c r="J233">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L233">
         <v>0</v>
@@ -8818,18 +8818,18 @@
     </row>
     <row r="234">
       <c r="A234">
-        <v>1982</v>
+        <v>1981</v>
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>GCL</t>
+          <t>SPR</t>
         </is>
       </c>
       <c r="C234">
-        <v>179420</v>
+        <v>139251</v>
       </c>
       <c r="E234">
-        <v>185085.6637001739</v>
+        <v>363578.929323775</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -8852,16 +8852,16 @@
         </is>
       </c>
       <c r="J234">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L234">
         <v>0</v>
       </c>
       <c r="M234">
-        <v>452601.0276631281</v>
+        <v>1038876.317981237</v>
       </c>
       <c r="N234">
-        <v>464820</v>
+        <v>410789</v>
       </c>
     </row>
     <row r="235">
@@ -8870,14 +8870,14 @@
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>SPR</t>
+          <t>GCL</t>
         </is>
       </c>
       <c r="C235">
-        <v>248700</v>
+        <v>179420</v>
       </c>
       <c r="E235">
-        <v>256553.3639629543</v>
+        <v>185085.6637001739</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -8900,7 +8900,7 @@
         </is>
       </c>
       <c r="J235">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L235">
         <v>0</v>
@@ -8914,18 +8914,18 @@
     </row>
     <row r="236">
       <c r="A236">
-        <v>1983</v>
+        <v>1982</v>
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>GCL</t>
+          <t>SPR</t>
         </is>
       </c>
       <c r="C236">
-        <v>348102</v>
+        <v>248700</v>
       </c>
       <c r="E236">
-        <v>508028.3034811231</v>
+        <v>256553.3639629543</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -8948,16 +8948,16 @@
         </is>
       </c>
       <c r="J236">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L236">
         <v>0</v>
       </c>
       <c r="M236">
-        <v>887925.5541521215</v>
+        <v>452601.0276631281</v>
       </c>
       <c r="N236">
-        <v>636512</v>
+        <v>464820</v>
       </c>
     </row>
     <row r="237">
@@ -8966,14 +8966,14 @@
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>SPR</t>
+          <t>GCL</t>
         </is>
       </c>
       <c r="C237">
-        <v>257410</v>
+        <v>348102</v>
       </c>
       <c r="E237">
-        <v>375670.2506709985</v>
+        <v>508028.3034811231</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -8996,7 +8996,7 @@
         </is>
       </c>
       <c r="J237">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L237">
         <v>0</v>
@@ -9010,18 +9010,18 @@
     </row>
     <row r="238">
       <c r="A238">
-        <v>1984</v>
+        <v>1983</v>
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>GCL</t>
+          <t>SPR</t>
         </is>
       </c>
       <c r="C238">
-        <v>133310</v>
+        <v>257410</v>
       </c>
       <c r="E238">
-        <v>518834.7686808587</v>
+        <v>375670.2506709985</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -9030,7 +9030,7 @@
       </c>
       <c r="G238" t="inlineStr">
         <is>
-          <t>commercial + FN catch records + creel survey</t>
+          <t>commercial + FN catch records</t>
         </is>
       </c>
       <c r="H238" t="inlineStr">
@@ -9044,16 +9044,16 @@
         </is>
       </c>
       <c r="J238">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L238">
         <v>0</v>
       </c>
       <c r="M238">
-        <v>945916</v>
+        <v>887925.5541521215</v>
       </c>
       <c r="N238">
-        <v>295810.0000000001</v>
+        <v>636512</v>
       </c>
     </row>
     <row r="239">
@@ -9062,14 +9062,14 @@
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>SPR</t>
+          <t>GCL</t>
         </is>
       </c>
       <c r="C239">
-        <v>89100.00000000001</v>
+        <v>133310</v>
       </c>
       <c r="E239">
-        <v>420949.2313191414</v>
+        <v>518834.7686808587</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -9092,7 +9092,7 @@
         </is>
       </c>
       <c r="J239">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L239">
         <v>0</v>
@@ -9106,18 +9106,18 @@
     </row>
     <row r="240">
       <c r="A240">
-        <v>1985</v>
+        <v>1984</v>
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>GCL</t>
+          <t>SPR</t>
         </is>
       </c>
       <c r="C240">
-        <v>120274</v>
+        <v>89100.00000000001</v>
       </c>
       <c r="E240">
-        <v>317599.9184047349</v>
+        <v>420949.2313191414</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -9140,16 +9140,16 @@
         </is>
       </c>
       <c r="J240">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L240">
         <v>0</v>
       </c>
       <c r="M240">
-        <v>458017.8992869732</v>
+        <v>945916</v>
       </c>
       <c r="N240">
-        <v>285725</v>
+        <v>295810.0000000001</v>
       </c>
     </row>
     <row r="241">
@@ -9158,14 +9158,14 @@
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>SPR</t>
+          <t>GCL</t>
         </is>
       </c>
       <c r="C241">
-        <v>146951</v>
+        <v>120274</v>
       </c>
       <c r="E241">
-        <v>139968.9808822382</v>
+        <v>317599.9184047349</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -9202,18 +9202,18 @@
     </row>
     <row r="242">
       <c r="A242">
-        <v>1986</v>
+        <v>1985</v>
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>GCL</t>
+          <t>SPR</t>
         </is>
       </c>
       <c r="C242">
-        <v>137807</v>
+        <v>146951</v>
       </c>
       <c r="E242">
-        <v>10315.74151293448</v>
+        <v>139968.9808822382</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -9242,10 +9242,10 @@
         <v>0</v>
       </c>
       <c r="M242">
-        <v>56948</v>
+        <v>458017.8992869732</v>
       </c>
       <c r="N242">
-        <v>334648</v>
+        <v>285725</v>
       </c>
     </row>
     <row r="243">
@@ -9254,14 +9254,14 @@
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>SPR</t>
+          <t>GCL</t>
         </is>
       </c>
       <c r="C243">
-        <v>192941</v>
+        <v>137807</v>
       </c>
       <c r="E243">
-        <v>46602.25848706553</v>
+        <v>10315.74151293448</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -9284,7 +9284,7 @@
         </is>
       </c>
       <c r="J243">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L243">
         <v>0</v>
@@ -9298,18 +9298,18 @@
     </row>
     <row r="244">
       <c r="A244">
-        <v>1987</v>
+        <v>1986</v>
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>GCL</t>
+          <t>SPR</t>
         </is>
       </c>
       <c r="C244">
-        <v>290714.9999999999</v>
+        <v>192941</v>
       </c>
       <c r="E244">
-        <v>83017.40213865854</v>
+        <v>46602.25848706553</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -9332,16 +9332,16 @@
         </is>
       </c>
       <c r="J244">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L244">
         <v>0</v>
       </c>
       <c r="M244">
-        <v>263260</v>
+        <v>56948</v>
       </c>
       <c r="N244">
-        <v>473349.9999999999</v>
+        <v>334648</v>
       </c>
     </row>
     <row r="245">
@@ -9350,14 +9350,14 @@
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>SPR</t>
+          <t>GCL</t>
         </is>
       </c>
       <c r="C245">
-        <v>151835</v>
+        <v>290714.9999999999</v>
       </c>
       <c r="E245">
-        <v>171365.5978613414</v>
+        <v>83017.40213865854</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -9380,7 +9380,7 @@
         </is>
       </c>
       <c r="J245">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L245">
         <v>0</v>
@@ -9394,18 +9394,18 @@
     </row>
     <row r="246">
       <c r="A246">
-        <v>1988</v>
+        <v>1987</v>
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>GCL</t>
+          <t>SPR</t>
         </is>
       </c>
       <c r="C246">
-        <v>206676.0000000001</v>
+        <v>151835</v>
       </c>
       <c r="E246">
-        <v>146833.0244309762</v>
+        <v>171365.5978613414</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -9428,16 +9428,16 @@
         </is>
       </c>
       <c r="J246">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L246">
         <v>0</v>
       </c>
       <c r="M246">
-        <v>326897.5916</v>
+        <v>263260</v>
       </c>
       <c r="N246">
-        <v>482393.0000000001</v>
+        <v>473349.9999999999</v>
       </c>
     </row>
     <row r="247">
@@ -9446,14 +9446,14 @@
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>SPR</t>
+          <t>GCL</t>
         </is>
       </c>
       <c r="C247">
-        <v>235417</v>
+        <v>206676.0000000001</v>
       </c>
       <c r="E247">
-        <v>178270.5671690238</v>
+        <v>146833.0244309762</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -9476,7 +9476,7 @@
         </is>
       </c>
       <c r="J247">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L247">
         <v>0</v>
@@ -9490,18 +9490,18 @@
     </row>
     <row r="248">
       <c r="A248">
-        <v>1989</v>
+        <v>1988</v>
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>GCL</t>
+          <t>SPR</t>
         </is>
       </c>
       <c r="C248">
-        <v>241263</v>
+        <v>235417</v>
       </c>
       <c r="E248">
-        <v>14924.00087526265</v>
+        <v>178270.5671690238</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -9524,16 +9524,16 @@
         </is>
       </c>
       <c r="J248">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L248">
         <v>0</v>
       </c>
       <c r="M248">
-        <v>28383.471375</v>
+        <v>326897.5916</v>
       </c>
       <c r="N248">
-        <v>449850.0000000001</v>
+        <v>482393.0000000001</v>
       </c>
     </row>
     <row r="249">
@@ -9542,14 +9542,14 @@
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>SPR</t>
+          <t>GCL</t>
         </is>
       </c>
       <c r="C249">
-        <v>167987</v>
+        <v>241263</v>
       </c>
       <c r="E249">
-        <v>13403.47049973735</v>
+        <v>14924.00087526265</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -9572,7 +9572,7 @@
         </is>
       </c>
       <c r="J249">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L249">
         <v>0</v>
@@ -9586,18 +9586,18 @@
     </row>
     <row r="250">
       <c r="A250">
-        <v>1990</v>
+        <v>1989</v>
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>GCL</t>
+          <t>SPR</t>
         </is>
       </c>
       <c r="C250">
-        <v>179091</v>
+        <v>167987</v>
       </c>
       <c r="E250">
-        <v>19353.20374687612</v>
+        <v>13403.47049973735</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -9620,16 +9620,16 @@
         </is>
       </c>
       <c r="J250">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L250">
         <v>0</v>
       </c>
       <c r="M250">
-        <v>37390</v>
+        <v>28383.471375</v>
       </c>
       <c r="N250">
-        <v>323281</v>
+        <v>449850.0000000001</v>
       </c>
     </row>
     <row r="251">
@@ -9638,14 +9638,14 @@
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>SPR</t>
+          <t>GCL</t>
         </is>
       </c>
       <c r="C251">
-        <v>112790</v>
+        <v>179091</v>
       </c>
       <c r="E251">
-        <v>17235.79625312387</v>
+        <v>19353.20374687612</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -9668,7 +9668,7 @@
         </is>
       </c>
       <c r="J251">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L251">
         <v>0</v>
@@ -9682,18 +9682,18 @@
     </row>
     <row r="252">
       <c r="A252">
-        <v>1991</v>
+        <v>1990</v>
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>GCL</t>
+          <t>SPR</t>
         </is>
       </c>
       <c r="C252">
-        <v>433390.0000000001</v>
+        <v>112790</v>
       </c>
       <c r="E252">
-        <v>807514.4757371147</v>
+        <v>17235.79625312387</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -9716,16 +9716,16 @@
         </is>
       </c>
       <c r="J252">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L252">
         <v>0</v>
       </c>
       <c r="M252">
-        <v>1181307</v>
+        <v>37390</v>
       </c>
       <c r="N252">
-        <v>680965.0000000001</v>
+        <v>323281</v>
       </c>
     </row>
     <row r="253">
@@ -9734,14 +9734,14 @@
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>SPR</t>
+          <t>GCL</t>
         </is>
       </c>
       <c r="C253">
-        <v>209475</v>
+        <v>433390.0000000001</v>
       </c>
       <c r="E253">
-        <v>362597.5242628853</v>
+        <v>807514.4757371147</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -9764,7 +9764,7 @@
         </is>
       </c>
       <c r="J253">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L253">
         <v>0</v>
@@ -9778,18 +9778,18 @@
     </row>
     <row r="254">
       <c r="A254">
-        <v>1992</v>
+        <v>1991</v>
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>GCL</t>
+          <t>SPR</t>
         </is>
       </c>
       <c r="C254">
-        <v>188153</v>
+        <v>209475</v>
       </c>
       <c r="E254">
-        <v>178554.8334567147</v>
+        <v>362597.5242628853</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -9812,16 +9812,16 @@
         </is>
       </c>
       <c r="J254">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L254">
         <v>0</v>
       </c>
       <c r="M254">
-        <v>579970.1466654321</v>
+        <v>1181307</v>
       </c>
       <c r="N254">
-        <v>437791</v>
+        <v>680965.0000000001</v>
       </c>
     </row>
     <row r="255">
@@ -9830,14 +9830,14 @@
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>SPR</t>
+          <t>GCL</t>
         </is>
       </c>
       <c r="C255">
-        <v>221937.9999999999</v>
+        <v>188153</v>
       </c>
       <c r="E255">
-        <v>392343.3132087174</v>
+        <v>178554.8334567147</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -9860,7 +9860,7 @@
         </is>
       </c>
       <c r="J255">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L255">
         <v>0</v>
@@ -9874,18 +9874,18 @@
     </row>
     <row r="256">
       <c r="A256">
-        <v>1993</v>
+        <v>1992</v>
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>GCL</t>
+          <t>SPR</t>
         </is>
       </c>
       <c r="C256">
-        <v>241761</v>
+        <v>221937.9999999999</v>
       </c>
       <c r="E256">
-        <v>432423.2165285624</v>
+        <v>392343.3132087174</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -9908,16 +9908,16 @@
         </is>
       </c>
       <c r="J256">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L256">
         <v>0</v>
       </c>
       <c r="M256">
-        <v>817369</v>
+        <v>579970.1466654321</v>
       </c>
       <c r="N256">
-        <v>627550</v>
+        <v>437791</v>
       </c>
     </row>
     <row r="257">
@@ -9926,14 +9926,14 @@
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>SPR</t>
+          <t>GCL</t>
         </is>
       </c>
       <c r="C257">
-        <v>205289</v>
+        <v>241761</v>
       </c>
       <c r="E257">
-        <v>348206.7834714376</v>
+        <v>432423.2165285624</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -9956,7 +9956,7 @@
         </is>
       </c>
       <c r="J257">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L257">
         <v>0</v>
@@ -9970,18 +9970,18 @@
     </row>
     <row r="258">
       <c r="A258">
-        <v>1994</v>
+        <v>1993</v>
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>GCL</t>
+          <t>SPR</t>
         </is>
       </c>
       <c r="C258">
-        <v>113493.0000000001</v>
+        <v>205289</v>
       </c>
       <c r="E258">
-        <v>97352.95948420328</v>
+        <v>348206.7834714376</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -10004,16 +10004,16 @@
         </is>
       </c>
       <c r="J258">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L258">
         <v>0</v>
       </c>
       <c r="M258">
-        <v>214571</v>
+        <v>817369</v>
       </c>
       <c r="N258">
-        <v>274663.0000000001</v>
+        <v>627550</v>
       </c>
     </row>
     <row r="259">
@@ -10022,14 +10022,14 @@
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>SPR</t>
+          <t>GCL</t>
         </is>
       </c>
       <c r="C259">
-        <v>143770.0000000001</v>
+        <v>113493.0000000001</v>
       </c>
       <c r="E259">
-        <v>82020.04051579669</v>
+        <v>97352.95948420328</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -10052,7 +10052,7 @@
         </is>
       </c>
       <c r="J259">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L259">
         <v>0</v>
@@ -10066,18 +10066,18 @@
     </row>
     <row r="260">
       <c r="A260">
-        <v>1995</v>
+        <v>1994</v>
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>GCL</t>
+          <t>SPR</t>
         </is>
       </c>
       <c r="C260">
-        <v>64011.00000000001</v>
+        <v>143770.0000000001</v>
       </c>
       <c r="E260">
-        <v>17925.29743190457</v>
+        <v>82020.04051579669</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -10100,16 +10100,16 @@
         </is>
       </c>
       <c r="J260">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L260">
         <v>0</v>
       </c>
       <c r="M260">
-        <v>30536.00420168067</v>
+        <v>214571</v>
       </c>
       <c r="N260">
-        <v>170811</v>
+        <v>274663.0000000001</v>
       </c>
     </row>
     <row r="261">
@@ -10118,14 +10118,14 @@
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>SPR</t>
+          <t>GCL</t>
         </is>
       </c>
       <c r="C261">
-        <v>102400</v>
+        <v>64011.00000000001</v>
       </c>
       <c r="E261">
-        <v>12521.7067697761</v>
+        <v>17925.29743190457</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -10148,7 +10148,7 @@
         </is>
       </c>
       <c r="J261">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L261">
         <v>0</v>
@@ -10162,18 +10162,18 @@
     </row>
     <row r="262">
       <c r="A262">
-        <v>1996</v>
+        <v>1995</v>
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>GCL</t>
+          <t>SPR</t>
         </is>
       </c>
       <c r="C262">
-        <v>186382</v>
+        <v>102400</v>
       </c>
       <c r="E262">
-        <v>26873.04375818335</v>
+        <v>12521.7067697761</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -10196,16 +10196,16 @@
         </is>
       </c>
       <c r="J262">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L262">
         <v>0</v>
       </c>
       <c r="M262">
-        <v>62596.00000000001</v>
+        <v>30536.00420168067</v>
       </c>
       <c r="N262">
-        <v>501780</v>
+        <v>170811</v>
       </c>
     </row>
     <row r="263">
@@ -10214,14 +10214,14 @@
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>SPR</t>
+          <t>GCL</t>
         </is>
       </c>
       <c r="C263">
-        <v>255498</v>
+        <v>186382</v>
       </c>
       <c r="E263">
-        <v>33811.95624181666</v>
+        <v>26873.04375818335</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -10244,7 +10244,7 @@
         </is>
       </c>
       <c r="J263">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L263">
         <v>0</v>
@@ -10258,18 +10258,18 @@
     </row>
     <row r="264">
       <c r="A264">
-        <v>1997</v>
+        <v>1996</v>
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>GCL</t>
+          <t>SPR</t>
         </is>
       </c>
       <c r="C264">
-        <v>178115.9999999999</v>
+        <v>255498</v>
       </c>
       <c r="E264">
-        <v>97280.64048682952</v>
+        <v>33811.95624181666</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -10283,7 +10283,7 @@
       </c>
       <c r="H264" t="inlineStr">
         <is>
-          <t>MLE run timing model</t>
+          <t>assumed run timing</t>
         </is>
       </c>
       <c r="I264" t="inlineStr">
@@ -10292,16 +10292,16 @@
         </is>
       </c>
       <c r="J264">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L264">
         <v>0</v>
       </c>
       <c r="M264">
-        <v>156384</v>
+        <v>62596.00000000001</v>
       </c>
       <c r="N264">
-        <v>356203.9999999999</v>
+        <v>501780</v>
       </c>
     </row>
     <row r="265">
@@ -10310,14 +10310,14 @@
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>SPR</t>
+          <t>GCL</t>
         </is>
       </c>
       <c r="C265">
-        <v>131888</v>
+        <v>178115.9999999999</v>
       </c>
       <c r="E265">
-        <v>45690.35951317049</v>
+        <v>97280.64048682952</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -10340,7 +10340,7 @@
         </is>
       </c>
       <c r="J265">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L265">
         <v>0</v>
@@ -10354,18 +10354,18 @@
     </row>
     <row r="266">
       <c r="A266">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>GCL</t>
+          <t>SPR</t>
         </is>
       </c>
       <c r="C266">
-        <v>274013.0000000001</v>
+        <v>131888</v>
       </c>
       <c r="E266">
-        <v>132609.2741320956</v>
+        <v>45690.35951317049</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -10388,16 +10388,16 @@
         </is>
       </c>
       <c r="J266">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L266">
         <v>0</v>
       </c>
       <c r="M266">
-        <v>235130.7241488512</v>
+        <v>156384</v>
       </c>
       <c r="N266">
-        <v>640127.0000000001</v>
+        <v>356203.9999999999</v>
       </c>
     </row>
     <row r="267">
@@ -10406,14 +10406,14 @@
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>SPR</t>
+          <t>GCL</t>
         </is>
       </c>
       <c r="C267">
-        <v>274014.0000000001</v>
+        <v>274013.0000000001</v>
       </c>
       <c r="E267">
-        <v>75320.45001675557</v>
+        <v>132609.2741320956</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -10436,7 +10436,7 @@
         </is>
       </c>
       <c r="J267">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L267">
         <v>0</v>
@@ -10450,18 +10450,18 @@
     </row>
     <row r="268">
       <c r="A268">
-        <v>1999</v>
+        <v>1998</v>
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>GCL</t>
+          <t>SPR</t>
         </is>
       </c>
       <c r="C268">
-        <v>211111.2792766747</v>
+        <v>274014.0000000001</v>
       </c>
       <c r="E268">
-        <v>58635.86069137148</v>
+        <v>75320.45001675557</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -10484,16 +10484,16 @@
         </is>
       </c>
       <c r="J268">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L268">
         <v>0</v>
       </c>
       <c r="M268">
-        <v>115856.068</v>
+        <v>235130.7241488512</v>
       </c>
       <c r="N268">
-        <v>394147.213702481</v>
+        <v>640127.0000000001</v>
       </c>
     </row>
     <row r="269">
@@ -10502,14 +10502,14 @@
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>SPR</t>
+          <t>GCL</t>
         </is>
       </c>
       <c r="C269">
-        <v>169635.9344258063</v>
+        <v>211111.2792766747</v>
       </c>
       <c r="E269">
-        <v>55911.20730862853</v>
+        <v>58635.86069137148</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -10532,7 +10532,7 @@
         </is>
       </c>
       <c r="J269">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L269">
         <v>0</v>
@@ -10546,18 +10546,18 @@
     </row>
     <row r="270">
       <c r="A270">
-        <v>2000</v>
+        <v>1999</v>
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>GCL</t>
+          <t>SPR</t>
         </is>
       </c>
       <c r="C270">
-        <v>71659.00000000004</v>
+        <v>169635.9344258063</v>
       </c>
       <c r="E270">
-        <v>37113.06465680368</v>
+        <v>55911.20730862853</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -10580,16 +10580,16 @@
         </is>
       </c>
       <c r="J270">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L270">
         <v>0</v>
       </c>
       <c r="M270">
-        <v>105163.5893782173</v>
+        <v>115856.068</v>
       </c>
       <c r="N270">
-        <v>223098.0000000001</v>
+        <v>394147.213702481</v>
       </c>
     </row>
     <row r="271">
@@ -10598,14 +10598,14 @@
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>SPR</t>
+          <t>GCL</t>
         </is>
       </c>
       <c r="C271">
-        <v>126339</v>
+        <v>71659.00000000004</v>
       </c>
       <c r="E271">
-        <v>67796.52472141362</v>
+        <v>37113.06465680368</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -10628,7 +10628,7 @@
         </is>
       </c>
       <c r="J271">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L271">
         <v>0</v>
@@ -10642,18 +10642,18 @@
     </row>
     <row r="272">
       <c r="A272">
-        <v>2001</v>
+        <v>2000</v>
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>GCL</t>
+          <t>SPR</t>
         </is>
       </c>
       <c r="C272">
-        <v>408826.862243237</v>
+        <v>126339</v>
       </c>
       <c r="E272">
-        <v>113863.9823215375</v>
+        <v>67796.52472141362</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -10676,16 +10676,16 @@
         </is>
       </c>
       <c r="J272">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L272">
         <v>0</v>
       </c>
       <c r="M272">
-        <v>233776.9205341995</v>
+        <v>105163.5893782173</v>
       </c>
       <c r="N272">
-        <v>800244.862243237</v>
+        <v>223098.0000000001</v>
       </c>
     </row>
     <row r="273">
@@ -10694,14 +10694,14 @@
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>SPR</t>
+          <t>GCL</t>
         </is>
       </c>
       <c r="C273">
-        <v>371518</v>
+        <v>408826.862243237</v>
       </c>
       <c r="E273">
-        <v>117872.9382126621</v>
+        <v>113863.9823215375</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -10724,7 +10724,7 @@
         </is>
       </c>
       <c r="J273">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L273">
         <v>0</v>
@@ -10738,18 +10738,18 @@
     </row>
     <row r="274">
       <c r="A274">
-        <v>2002</v>
+        <v>2001</v>
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>GCL</t>
+          <t>SPR</t>
         </is>
       </c>
       <c r="C274">
-        <v>284855.7806640533</v>
+        <v>371518</v>
       </c>
       <c r="E274">
-        <v>384591.3972696845</v>
+        <v>117872.9382126621</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -10772,16 +10772,16 @@
         </is>
       </c>
       <c r="J274">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L274">
         <v>0</v>
       </c>
       <c r="M274">
-        <v>600455.7875803118</v>
+        <v>233776.9205341995</v>
       </c>
       <c r="N274">
-        <v>522744.7806640534</v>
+        <v>800244.862243237</v>
       </c>
     </row>
     <row r="275">
@@ -10790,14 +10790,14 @@
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>SPR</t>
+          <t>GCL</t>
         </is>
       </c>
       <c r="C275">
-        <v>220189.0000000001</v>
+        <v>284855.7806640533</v>
       </c>
       <c r="E275">
-        <v>211952.3903106272</v>
+        <v>384591.3972696845</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -10820,7 +10820,7 @@
         </is>
       </c>
       <c r="J275">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L275">
         <v>0</v>
@@ -10834,18 +10834,18 @@
     </row>
     <row r="276">
       <c r="A276">
-        <v>2003</v>
+        <v>2002</v>
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>GCL</t>
+          <t>SPR</t>
         </is>
       </c>
       <c r="C276">
-        <v>250967.6307078648</v>
+        <v>220189.0000000001</v>
       </c>
       <c r="E276">
-        <v>276616.6663030458</v>
+        <v>211952.3903106272</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -10868,16 +10868,16 @@
         </is>
       </c>
       <c r="J276">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L276">
         <v>0</v>
       </c>
       <c r="M276">
-        <v>531341.3718806775</v>
+        <v>600455.7875803118</v>
       </c>
       <c r="N276">
-        <v>443175.6307078647</v>
+        <v>522744.7806640534</v>
       </c>
     </row>
     <row r="277">
@@ -10886,14 +10886,14 @@
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>SPR</t>
+          <t>GCL</t>
         </is>
       </c>
       <c r="C277">
-        <v>188907.9999999999</v>
+        <v>250967.6307078648</v>
       </c>
       <c r="E277">
-        <v>254487.7055776317</v>
+        <v>276616.6663030458</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -10916,7 +10916,7 @@
         </is>
       </c>
       <c r="J277">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L277">
         <v>0</v>
@@ -10930,18 +10930,18 @@
     </row>
     <row r="278">
       <c r="A278">
-        <v>2004</v>
+        <v>2003</v>
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>GCL</t>
+          <t>SPR</t>
         </is>
       </c>
       <c r="C278">
-        <v>224638</v>
+        <v>188907.9999999999</v>
       </c>
       <c r="E278">
-        <v>202386.6849503428</v>
+        <v>254487.7055776317</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -10964,16 +10964,16 @@
         </is>
       </c>
       <c r="J278">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L278">
         <v>0</v>
       </c>
       <c r="M278">
-        <v>334435.1661</v>
+        <v>531341.3718806775</v>
       </c>
       <c r="N278">
-        <v>377681</v>
+        <v>443175.6307078647</v>
       </c>
     </row>
     <row r="279">
@@ -10982,14 +10982,14 @@
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>SPR</t>
+          <t>GCL</t>
         </is>
       </c>
       <c r="C279">
-        <v>150443</v>
+        <v>224638</v>
       </c>
       <c r="E279">
-        <v>132038.4811496573</v>
+        <v>202386.6849503428</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -11012,7 +11012,7 @@
         </is>
       </c>
       <c r="J279">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L279">
         <v>0</v>
@@ -11026,18 +11026,18 @@
     </row>
     <row r="280">
       <c r="A280">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>GCL</t>
+          <t>SPR</t>
         </is>
       </c>
       <c r="C280">
-        <v>194678.1407832186</v>
+        <v>150443</v>
       </c>
       <c r="E280">
-        <v>63306.91610701918</v>
+        <v>132038.4811496573</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -11060,16 +11060,16 @@
         </is>
       </c>
       <c r="J280">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L280">
         <v>0</v>
       </c>
       <c r="M280">
-        <v>105345.3813728291</v>
+        <v>334435.1661</v>
       </c>
       <c r="N280">
-        <v>347117.1404960908</v>
+        <v>377681</v>
       </c>
     </row>
     <row r="281">
@@ -11078,14 +11078,14 @@
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>SPR</t>
+          <t>GCL</t>
         </is>
       </c>
       <c r="C281">
-        <v>151138.9997128722</v>
+        <v>194678.1407832186</v>
       </c>
       <c r="E281">
-        <v>41737.46526580991</v>
+        <v>63306.91610701918</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -11108,7 +11108,7 @@
         </is>
       </c>
       <c r="J281">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L281">
         <v>0</v>
@@ -11122,18 +11122,18 @@
     </row>
     <row r="282">
       <c r="A282">
-        <v>2006</v>
+        <v>2005</v>
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>GCL</t>
+          <t>SPR</t>
         </is>
       </c>
       <c r="C282">
-        <v>136246.7296855859</v>
+        <v>151138.9997128722</v>
       </c>
       <c r="E282">
-        <v>61287.76745850981</v>
+        <v>41737.46526580991</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -11156,16 +11156,16 @@
         </is>
       </c>
       <c r="J282">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L282">
         <v>0</v>
       </c>
       <c r="M282">
-        <v>90500.48540000001</v>
+        <v>105345.3813728291</v>
       </c>
       <c r="N282">
-        <v>203635.7296855859</v>
+        <v>347117.1404960908</v>
       </c>
     </row>
     <row r="283">
@@ -11174,14 +11174,14 @@
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>SPR</t>
+          <t>GCL</t>
         </is>
       </c>
       <c r="C283">
-        <v>63788.99999999998</v>
+        <v>136246.7296855859</v>
       </c>
       <c r="E283">
-        <v>28915.71794149018</v>
+        <v>61287.76745850981</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -11204,7 +11204,7 @@
         </is>
       </c>
       <c r="J283">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L283">
         <v>0</v>
@@ -11218,18 +11218,18 @@
     </row>
     <row r="284">
       <c r="A284">
-        <v>2007</v>
+        <v>2006</v>
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>GCL</t>
+          <t>SPR</t>
         </is>
       </c>
       <c r="C284">
-        <v>77622.00000000004</v>
+        <v>63788.99999999998</v>
       </c>
       <c r="E284">
-        <v>5003.304152842727</v>
+        <v>28915.71794149018</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -11252,16 +11252,16 @@
         </is>
       </c>
       <c r="J284">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L284">
         <v>0</v>
       </c>
       <c r="M284">
-        <v>10040</v>
+        <v>90500.48540000001</v>
       </c>
       <c r="N284">
-        <v>162815.0000000001</v>
+        <v>203635.7296855859</v>
       </c>
     </row>
     <row r="285">
@@ -11270,14 +11270,14 @@
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>SPR</t>
+          <t>GCL</t>
         </is>
       </c>
       <c r="C285">
-        <v>72693</v>
+        <v>77622.00000000004</v>
       </c>
       <c r="E285">
-        <v>4755.695847157274</v>
+        <v>5003.304152842727</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -11300,7 +11300,7 @@
         </is>
       </c>
       <c r="J285">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L285">
         <v>0</v>
@@ -11314,22 +11314,22 @@
     </row>
     <row r="286">
       <c r="A286">
-        <v>2008</v>
+        <v>2007</v>
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>GCL</t>
+          <t>SPR</t>
         </is>
       </c>
       <c r="C286">
-        <v>74024.00675675675</v>
+        <v>72693</v>
       </c>
       <c r="E286">
-        <v>0</v>
+        <v>4755.695847157274</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
-          <t>video counts</t>
+          <t>resistivity counter</t>
         </is>
       </c>
       <c r="G286" t="inlineStr">
@@ -11339,7 +11339,7 @@
       </c>
       <c r="H286" t="inlineStr">
         <is>
-          <t>escapement</t>
+          <t>MLE run timing model</t>
         </is>
       </c>
       <c r="I286" t="inlineStr">
@@ -11348,16 +11348,16 @@
         </is>
       </c>
       <c r="J286">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L286">
         <v>0</v>
       </c>
       <c r="M286">
-        <v>0</v>
+        <v>10040</v>
       </c>
       <c r="N286">
-        <v>203968.0067567567</v>
+        <v>162815.0000000001</v>
       </c>
     </row>
     <row r="287">
@@ -11366,11 +11366,11 @@
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>SPR</t>
+          <t>GCL</t>
         </is>
       </c>
       <c r="C287">
-        <v>116844</v>
+        <v>74024.00675675675</v>
       </c>
       <c r="E287">
         <v>0</v>
@@ -11396,7 +11396,7 @@
         </is>
       </c>
       <c r="J287">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L287">
         <v>0</v>
@@ -11410,18 +11410,18 @@
     </row>
     <row r="288">
       <c r="A288">
-        <v>2009</v>
+        <v>2008</v>
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>GCL</t>
+          <t>SPR</t>
         </is>
       </c>
       <c r="C288">
-        <v>222241.2876649233</v>
+        <v>116844</v>
       </c>
       <c r="E288">
-        <v>86640.18459735703</v>
+        <v>0</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -11435,7 +11435,7 @@
       </c>
       <c r="H288" t="inlineStr">
         <is>
-          <t>assumed run timing</t>
+          <t>escapement</t>
         </is>
       </c>
       <c r="I288" t="inlineStr">
@@ -11444,16 +11444,16 @@
         </is>
       </c>
       <c r="J288">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L288">
         <v>0</v>
       </c>
       <c r="M288">
-        <v>149521.6328902802</v>
+        <v>0</v>
       </c>
       <c r="N288">
-        <v>430072.2876649234</v>
+        <v>203968.0067567567</v>
       </c>
     </row>
     <row r="289">
@@ -11462,14 +11462,14 @@
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>SPR</t>
+          <t>GCL</t>
         </is>
       </c>
       <c r="C289">
-        <v>177831.0000000001</v>
+        <v>222241.2876649233</v>
       </c>
       <c r="E289">
-        <v>62881.44829292317</v>
+        <v>86640.18459735703</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -11492,7 +11492,7 @@
         </is>
       </c>
       <c r="J289">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L289">
         <v>0</v>
@@ -11506,18 +11506,18 @@
     </row>
     <row r="290">
       <c r="A290">
-        <v>2010</v>
+        <v>2009</v>
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>GCL</t>
+          <t>SPR</t>
         </is>
       </c>
       <c r="C290">
-        <v>343999</v>
+        <v>177831.0000000001</v>
       </c>
       <c r="E290">
-        <v>496565.0420667162</v>
+        <v>62881.44829292317</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -11540,16 +11540,16 @@
         </is>
       </c>
       <c r="J290">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L290">
         <v>0</v>
       </c>
       <c r="M290">
-        <v>938124.682827242</v>
+        <v>149521.6328902802</v>
       </c>
       <c r="N290">
-        <v>830435</v>
+        <v>430072.2876649234</v>
       </c>
     </row>
     <row r="291">
@@ -11558,14 +11558,14 @@
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>SPR</t>
+          <t>GCL</t>
         </is>
       </c>
       <c r="C291">
-        <v>456436.0000000001</v>
+        <v>343999</v>
       </c>
       <c r="E291">
-        <v>441559.6407605257</v>
+        <v>496565.0420667162</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -11588,7 +11588,7 @@
         </is>
       </c>
       <c r="J291">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L291">
         <v>0</v>
@@ -11602,18 +11602,18 @@
     </row>
     <row r="292">
       <c r="A292">
-        <v>2011</v>
+        <v>2010</v>
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>GCL</t>
+          <t>SPR</t>
         </is>
       </c>
       <c r="C292">
-        <v>445819.9999999999</v>
+        <v>456436.0000000001</v>
       </c>
       <c r="E292">
-        <v>321344.7875944228</v>
+        <v>441559.6407605257</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -11627,7 +11627,7 @@
       </c>
       <c r="H292" t="inlineStr">
         <is>
-          <t>DNA attribution</t>
+          <t>assumed run timing</t>
         </is>
       </c>
       <c r="I292" t="inlineStr">
@@ -11636,16 +11636,16 @@
         </is>
       </c>
       <c r="J292">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L292">
         <v>0</v>
       </c>
       <c r="M292">
-        <v>590914.3653989306</v>
+        <v>938124.682827242</v>
       </c>
       <c r="N292">
-        <v>905456.9999999998</v>
+        <v>830435</v>
       </c>
     </row>
     <row r="293">
@@ -11654,14 +11654,14 @@
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>SPR</t>
+          <t>GCL</t>
         </is>
       </c>
       <c r="C293">
-        <v>439213.9999999999</v>
+        <v>445819.9999999999</v>
       </c>
       <c r="E293">
-        <v>262604.5778045079</v>
+        <v>321344.7875944228</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -11684,7 +11684,7 @@
         </is>
       </c>
       <c r="J293">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L293">
         <v>0</v>
@@ -11698,18 +11698,18 @@
     </row>
     <row r="294">
       <c r="A294">
-        <v>2012</v>
+        <v>2011</v>
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>GCL</t>
+          <t>SPR</t>
         </is>
       </c>
       <c r="C294">
-        <v>149343.9999999999</v>
+        <v>439213.9999999999</v>
       </c>
       <c r="E294">
-        <v>181516.9165734799</v>
+        <v>262604.5778045079</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -11732,16 +11732,16 @@
         </is>
       </c>
       <c r="J294">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L294">
         <v>0</v>
       </c>
       <c r="M294">
-        <v>385592.5588652157</v>
+        <v>590914.3653989306</v>
       </c>
       <c r="N294">
-        <v>395857.9999999999</v>
+        <v>905456.9999999998</v>
       </c>
     </row>
     <row r="295">
@@ -11750,14 +11750,14 @@
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>SPR</t>
+          <t>GCL</t>
         </is>
       </c>
       <c r="C295">
-        <v>229381</v>
+        <v>149343.9999999999</v>
       </c>
       <c r="E295">
-        <v>198133.6422917358</v>
+        <v>181516.9165734799</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -11780,7 +11780,7 @@
         </is>
       </c>
       <c r="J295">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L295">
         <v>0</v>
@@ -11794,18 +11794,18 @@
     </row>
     <row r="296">
       <c r="A296">
-        <v>2013</v>
+        <v>2012</v>
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>GCL</t>
+          <t>SPR</t>
         </is>
       </c>
       <c r="C296">
-        <v>184732.5000000001</v>
+        <v>229381</v>
       </c>
       <c r="E296">
-        <v>26580.1391093958</v>
+        <v>198133.6422917358</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -11828,16 +11828,16 @@
         </is>
       </c>
       <c r="J296">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L296">
         <v>0</v>
       </c>
       <c r="M296">
-        <v>89406.92896357566</v>
+        <v>385592.5588652157</v>
       </c>
       <c r="N296">
-        <v>664957.5864587885</v>
+        <v>395857.9999999999</v>
       </c>
     </row>
     <row r="297">
@@ -11846,14 +11846,14 @@
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>SPR</t>
+          <t>GCL</t>
         </is>
       </c>
       <c r="C297">
-        <v>467725.0864587884</v>
+        <v>184732.5000000001</v>
       </c>
       <c r="E297">
-        <v>61701.78985417985</v>
+        <v>26580.1391093958</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -11876,7 +11876,7 @@
         </is>
       </c>
       <c r="J297">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L297">
         <v>0</v>
@@ -11890,18 +11890,18 @@
     </row>
     <row r="298">
       <c r="A298">
-        <v>2014</v>
+        <v>2013</v>
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>GCL</t>
+          <t>SPR</t>
         </is>
       </c>
       <c r="C298">
-        <v>162685.7579745326</v>
+        <v>467725.0864587884</v>
       </c>
       <c r="E298">
-        <v>191765.2559201121</v>
+        <v>61701.78985417985</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -11924,16 +11924,16 @@
         </is>
       </c>
       <c r="J298">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L298">
         <v>0</v>
       </c>
       <c r="M298">
-        <v>676503.3420213063</v>
+        <v>89406.92896357566</v>
       </c>
       <c r="N298">
-        <v>539951.848459169</v>
+        <v>664957.5864587885</v>
       </c>
     </row>
     <row r="299">
@@ -11942,14 +11942,14 @@
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>SPR</t>
+          <t>GCL</t>
         </is>
       </c>
       <c r="C299">
-        <v>365429.0904846364</v>
+        <v>162685.7579745326</v>
       </c>
       <c r="E299">
-        <v>463082.0861011941</v>
+        <v>191765.2559201121</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -11972,7 +11972,7 @@
         </is>
       </c>
       <c r="J299">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L299">
         <v>0</v>
@@ -11986,18 +11986,18 @@
     </row>
     <row r="300">
       <c r="A300">
-        <v>2015</v>
+        <v>2014</v>
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>GCL</t>
+          <t>SPR</t>
         </is>
       </c>
       <c r="C300">
-        <v>427539.0700000001</v>
+        <v>365429.0904846364</v>
       </c>
       <c r="E300">
-        <v>576323</v>
+        <v>463082.0861011941</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -12020,16 +12020,16 @@
         </is>
       </c>
       <c r="J300">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L300">
         <v>0</v>
       </c>
       <c r="M300">
-        <v>1309599</v>
+        <v>676503.3420213063</v>
       </c>
       <c r="N300">
-        <v>764186.6399999999</v>
+        <v>539951.848459169</v>
       </c>
     </row>
     <row r="301">
@@ -12038,14 +12038,14 @@
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>SPR</t>
+          <t>GCL</t>
         </is>
       </c>
       <c r="C301">
-        <v>330247.5699999999</v>
+        <v>427539.0700000001</v>
       </c>
       <c r="E301">
-        <v>728084</v>
+        <v>576323</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -12068,7 +12068,7 @@
         </is>
       </c>
       <c r="J301">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L301">
         <v>0</v>
@@ -12082,18 +12082,18 @@
     </row>
     <row r="302">
       <c r="A302">
-        <v>2016</v>
+        <v>2015</v>
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>GCL</t>
+          <t>SPR</t>
         </is>
       </c>
       <c r="C302">
-        <v>224362.26</v>
+        <v>330247.5699999999</v>
       </c>
       <c r="E302">
-        <v>346601</v>
+        <v>728084</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -12116,16 +12116,16 @@
         </is>
       </c>
       <c r="J302">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L302">
         <v>0</v>
       </c>
       <c r="M302">
-        <v>662128</v>
+        <v>1309599</v>
       </c>
       <c r="N302">
-        <v>468215.01</v>
+        <v>764186.6399999999</v>
       </c>
     </row>
     <row r="303">
@@ -12134,14 +12134,14 @@
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>SPR</t>
+          <t>GCL</t>
         </is>
       </c>
       <c r="C303">
-        <v>233152.75</v>
+        <v>224362.26</v>
       </c>
       <c r="E303">
-        <v>292416</v>
+        <v>346601</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -12164,7 +12164,7 @@
         </is>
       </c>
       <c r="J303">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L303">
         <v>0</v>
@@ -12178,18 +12178,18 @@
     </row>
     <row r="304">
       <c r="A304">
-        <v>2017</v>
+        <v>2016</v>
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>GCL</t>
+          <t>SPR</t>
         </is>
       </c>
       <c r="C304">
-        <v>138816.9999999999</v>
+        <v>233152.75</v>
       </c>
       <c r="E304">
-        <v>35952.90842462306</v>
+        <v>292416</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -12212,16 +12212,16 @@
         </is>
       </c>
       <c r="J304">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L304">
         <v>0</v>
       </c>
       <c r="M304">
-        <v>97288.52343308111</v>
+        <v>662128</v>
       </c>
       <c r="N304">
-        <v>457992.6800000002</v>
+        <v>468215.01</v>
       </c>
     </row>
     <row r="305">
@@ -12230,14 +12230,14 @@
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>SPR</t>
+          <t>GCL</t>
         </is>
       </c>
       <c r="C305">
-        <v>296471.6800000002</v>
+        <v>138816.9999999999</v>
       </c>
       <c r="E305">
-        <v>58118.61500845804</v>
+        <v>35952.90842462306</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -12260,7 +12260,7 @@
         </is>
       </c>
       <c r="J305">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L305">
         <v>0</v>
@@ -12274,18 +12274,18 @@
     </row>
     <row r="306">
       <c r="A306">
-        <v>2018</v>
+        <v>2017</v>
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>GCL</t>
+          <t>SPR</t>
         </is>
       </c>
       <c r="C306">
-        <v>38619.78999999999</v>
+        <v>296471.6800000002</v>
       </c>
       <c r="E306">
-        <v>15271.24414467358</v>
+        <v>58118.61500845804</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -12308,16 +12308,16 @@
         </is>
       </c>
       <c r="J306">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L306">
         <v>0</v>
       </c>
       <c r="M306">
-        <v>82158.61597752468</v>
+        <v>97288.52343308111</v>
       </c>
       <c r="N306">
-        <v>208635.1100000002</v>
+        <v>457992.6800000002</v>
       </c>
     </row>
     <row r="307">
@@ -12326,14 +12326,14 @@
       </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t>SPR</t>
+          <t>GCL</t>
         </is>
       </c>
       <c r="C307">
-        <v>157812.3200000002</v>
+        <v>38619.78999999999</v>
       </c>
       <c r="E307">
-        <v>66261.3718328511</v>
+        <v>15271.24414467358</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -12356,7 +12356,7 @@
         </is>
       </c>
       <c r="J307">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L307">
         <v>0</v>
@@ -12370,18 +12370,18 @@
     </row>
     <row r="308">
       <c r="A308">
-        <v>2019</v>
+        <v>2018</v>
       </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t>GCL</t>
+          <t>SPR</t>
         </is>
       </c>
       <c r="C308">
-        <v>48820.01</v>
+        <v>157812.3200000002</v>
       </c>
       <c r="E308">
-        <v>14863.06220666183</v>
+        <v>66261.3718328511</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -12404,16 +12404,16 @@
         </is>
       </c>
       <c r="J308">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L308">
         <v>0</v>
       </c>
       <c r="M308">
-        <v>54797.43787213185</v>
+        <v>82158.61597752468</v>
       </c>
       <c r="N308">
-        <v>191725.02</v>
+        <v>208635.1100000002</v>
       </c>
     </row>
     <row r="309">
@@ -12422,14 +12422,14 @@
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>SPR</t>
+          <t>GCL</t>
         </is>
       </c>
       <c r="C309">
-        <v>129356.01</v>
+        <v>48820.01</v>
       </c>
       <c r="E309">
-        <v>39780.37566547002</v>
+        <v>14863.06220666183</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -12452,7 +12452,7 @@
         </is>
       </c>
       <c r="J309">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L309">
         <v>0</v>
@@ -12466,18 +12466,18 @@
     </row>
     <row r="310">
       <c r="A310">
-        <v>2020</v>
+        <v>2019</v>
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>GCL</t>
+          <t>SPR</t>
         </is>
       </c>
       <c r="C310">
-        <v>139976.06</v>
+        <v>129356.01</v>
       </c>
       <c r="E310">
-        <v>34161.94953692595</v>
+        <v>39780.37566547002</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -12500,16 +12500,16 @@
         </is>
       </c>
       <c r="J310">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L310">
         <v>0</v>
       </c>
       <c r="M310">
-        <v>74112.09621734613</v>
+        <v>54797.43787213185</v>
       </c>
       <c r="N310">
-        <v>314010.15</v>
+        <v>191725.02</v>
       </c>
     </row>
     <row r="311">
@@ -12518,14 +12518,14 @@
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>SPR</t>
+          <t>GCL</t>
         </is>
       </c>
       <c r="C311">
-        <v>169445.09</v>
+        <v>139976.06</v>
       </c>
       <c r="E311">
-        <v>39507.14668042018</v>
+        <v>34161.94953692595</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -12548,7 +12548,7 @@
         </is>
       </c>
       <c r="J311">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L311">
         <v>0</v>
@@ -12562,18 +12562,18 @@
     </row>
     <row r="312">
       <c r="A312">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>GCL</t>
+          <t>SPR</t>
         </is>
       </c>
       <c r="C312">
-        <v>225180</v>
+        <v>169445.09</v>
       </c>
       <c r="E312">
-        <v>113676</v>
+        <v>39507.14668042018</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -12596,16 +12596,16 @@
         </is>
       </c>
       <c r="J312">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L312">
         <v>0</v>
       </c>
       <c r="M312">
-        <v>187163</v>
+        <v>74112.09621734613</v>
       </c>
       <c r="N312">
-        <v>422040</v>
+        <v>314010.15</v>
       </c>
     </row>
     <row r="313">
@@ -12614,14 +12614,14 @@
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>SPR</t>
+          <t>GCL</t>
         </is>
       </c>
       <c r="C313">
-        <v>182340</v>
+        <v>225180</v>
       </c>
       <c r="E313">
-        <v>69128</v>
+        <v>113676</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -12644,7 +12644,7 @@
         </is>
       </c>
       <c r="J313">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L313">
         <v>0</v>
@@ -12658,18 +12658,18 @@
     </row>
     <row r="314">
       <c r="A314">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>GCL</t>
+          <t>SPR</t>
         </is>
       </c>
       <c r="C314">
-        <v>235763</v>
+        <v>182340</v>
       </c>
       <c r="E314">
-        <v>110012</v>
+        <v>69128</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -12692,16 +12692,16 @@
         </is>
       </c>
       <c r="J314">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L314">
         <v>0</v>
       </c>
       <c r="M314">
-        <v>351689</v>
+        <v>187163</v>
       </c>
       <c r="N314">
-        <v>669650</v>
+        <v>422040</v>
       </c>
     </row>
     <row r="315">
@@ -12710,14 +12710,14 @@
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>SPR</t>
+          <t>GCL</t>
         </is>
       </c>
       <c r="C315">
-        <v>415241</v>
+        <v>235763</v>
       </c>
       <c r="E315">
-        <v>233946</v>
+        <v>110012</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -12740,7 +12740,7 @@
         </is>
       </c>
       <c r="J315">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L315">
         <v>0</v>
@@ -12754,18 +12754,18 @@
     </row>
     <row r="316">
       <c r="A316">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>GCL</t>
+          <t>SPR</t>
         </is>
       </c>
       <c r="C316">
-        <v>209265.0000000001</v>
+        <v>415241</v>
       </c>
       <c r="E316">
-        <v>141594.4059457992</v>
+        <v>233946</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -12788,16 +12788,16 @@
         </is>
       </c>
       <c r="J316">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L316">
         <v>0</v>
       </c>
       <c r="M316">
-        <v>328495.6625937843</v>
+        <v>351689</v>
       </c>
       <c r="N316">
-        <v>377396.0000000001</v>
+        <v>669650</v>
       </c>
     </row>
     <row r="317">
@@ -12806,14 +12806,14 @@
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>SPR</t>
+          <t>GCL</t>
         </is>
       </c>
       <c r="C317">
-        <v>155018</v>
+        <v>209265.0000000001</v>
       </c>
       <c r="E317">
-        <v>178705.2566479851</v>
+        <v>141594.4059457992</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -12836,7 +12836,7 @@
         </is>
       </c>
       <c r="J317">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L317">
         <v>0</v>
@@ -12850,18 +12850,18 @@
     </row>
     <row r="318">
       <c r="A318">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>GCL</t>
+          <t>SPR</t>
         </is>
       </c>
       <c r="C318">
-        <v>373658.9999999998</v>
+        <v>155018</v>
       </c>
       <c r="E318">
-        <v>211678.0913601878</v>
+        <v>178705.2566479851</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -12884,16 +12884,16 @@
         </is>
       </c>
       <c r="J318">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L318">
         <v>0</v>
       </c>
       <c r="M318">
-        <v>290214.7871306904</v>
+        <v>328495.6625937843</v>
       </c>
       <c r="N318">
-        <v>497190.9999999999</v>
+        <v>377396.0000000001</v>
       </c>
     </row>
     <row r="319">
@@ -12902,14 +12902,14 @@
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>SPR</t>
+          <t>GCL</t>
         </is>
       </c>
       <c r="C319">
-        <v>119995</v>
+        <v>373658.9999999998</v>
       </c>
       <c r="E319">
-        <v>73767.6957705026</v>
+        <v>211678.0913601878</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -12932,7 +12932,7 @@
         </is>
       </c>
       <c r="J319">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L319">
         <v>0</v>
@@ -12946,65 +12946,155 @@
     </row>
     <row r="320">
       <c r="A320">
-        <v>1903</v>
+        <v>2024</v>
       </c>
       <c r="B320" t="inlineStr">
         <is>
-          <t>GCL + SPR</t>
+          <t>SPR</t>
+        </is>
+      </c>
+      <c r="C320">
+        <v>119995</v>
+      </c>
+      <c r="E320">
+        <v>73767.6957705026</v>
+      </c>
+      <c r="F320" t="inlineStr">
+        <is>
+          <t>video counts</t>
         </is>
       </c>
       <c r="G320" t="inlineStr">
         <is>
-          <t>cannery pack</t>
-        </is>
+          <t>commercial + FN catch records + creel survey</t>
+        </is>
+      </c>
+      <c r="H320" t="inlineStr">
+        <is>
+          <t>DNA attribution</t>
+        </is>
+      </c>
+      <c r="I320" t="inlineStr">
+        <is>
+          <t>scale sampling</t>
+        </is>
+      </c>
+      <c r="J320">
+        <v>0</v>
+      </c>
+      <c r="L320">
+        <v>0</v>
       </c>
       <c r="M320">
-        <v>44070</v>
+        <v>290214.7871306904</v>
+      </c>
+      <c r="N320">
+        <v>497190.9999999999</v>
       </c>
     </row>
     <row r="321">
       <c r="A321">
-        <v>1903</v>
+        <v>2025</v>
       </c>
       <c r="B321" t="inlineStr">
         <is>
-          <t>HUC</t>
+          <t>GCL</t>
+        </is>
+      </c>
+      <c r="C321">
+        <v>447617</v>
+      </c>
+      <c r="E321">
+        <v>233609</v>
+      </c>
+      <c r="F321" t="inlineStr">
+        <is>
+          <t>video counts</t>
         </is>
       </c>
       <c r="G321" t="inlineStr">
         <is>
-          <t>cannery pack</t>
-        </is>
+          <t>commercial + FN catch records + creel survey</t>
+        </is>
+      </c>
+      <c r="H321" t="inlineStr">
+        <is>
+          <t>DNA attribution</t>
+        </is>
+      </c>
+      <c r="I321" t="inlineStr">
+        <is>
+          <t>scale sampling</t>
+        </is>
+      </c>
+      <c r="J321">
+        <v>1</v>
+      </c>
+      <c r="L321">
+        <v>0</v>
       </c>
       <c r="M321">
-        <v>44070</v>
+        <v>294097</v>
+      </c>
+      <c r="N321">
+        <v>569894</v>
       </c>
     </row>
     <row r="322">
       <c r="A322">
-        <v>1904</v>
+        <v>2025</v>
       </c>
       <c r="B322" t="inlineStr">
         <is>
-          <t>GCL + SPR</t>
+          <t>SPR</t>
+        </is>
+      </c>
+      <c r="C322">
+        <v>106313</v>
+      </c>
+      <c r="E322">
+        <v>55565</v>
+      </c>
+      <c r="F322" t="inlineStr">
+        <is>
+          <t>video counts</t>
         </is>
       </c>
       <c r="G322" t="inlineStr">
         <is>
-          <t>cannery pack</t>
-        </is>
+          <t>commercial + FN catch records + creel survey</t>
+        </is>
+      </c>
+      <c r="H322" t="inlineStr">
+        <is>
+          <t>DNA attribution</t>
+        </is>
+      </c>
+      <c r="I322" t="inlineStr">
+        <is>
+          <t>scale sampling</t>
+        </is>
+      </c>
+      <c r="J322">
+        <v>0</v>
+      </c>
+      <c r="L322">
+        <v>0</v>
       </c>
       <c r="M322">
-        <v>44590</v>
+        <v>294097</v>
+      </c>
+      <c r="N322">
+        <v>569894</v>
       </c>
     </row>
     <row r="323">
       <c r="A323">
-        <v>1904</v>
+        <v>1903</v>
       </c>
       <c r="B323" t="inlineStr">
         <is>
-          <t>HUC</t>
+          <t>GCL + SPR</t>
         </is>
       </c>
       <c r="G323" t="inlineStr">
@@ -13013,16 +13103,16 @@
         </is>
       </c>
       <c r="M323">
-        <v>44590</v>
+        <v>44070</v>
       </c>
     </row>
     <row r="324">
       <c r="A324">
-        <v>1905</v>
+        <v>1903</v>
       </c>
       <c r="B324" t="inlineStr">
         <is>
-          <t>GCL + SPR</t>
+          <t>HUC</t>
         </is>
       </c>
       <c r="G324" t="inlineStr">
@@ -13031,16 +13121,16 @@
         </is>
       </c>
       <c r="M324">
-        <v>24440</v>
+        <v>44070</v>
       </c>
     </row>
     <row r="325">
       <c r="A325">
-        <v>1905</v>
+        <v>1904</v>
       </c>
       <c r="B325" t="inlineStr">
         <is>
-          <t>HUC</t>
+          <t>GCL + SPR</t>
         </is>
       </c>
       <c r="G325" t="inlineStr">
@@ -13049,16 +13139,16 @@
         </is>
       </c>
       <c r="M325">
-        <v>24440</v>
+        <v>44590</v>
       </c>
     </row>
     <row r="326">
       <c r="A326">
-        <v>1906</v>
+        <v>1904</v>
       </c>
       <c r="B326" t="inlineStr">
         <is>
-          <t>GCL + SPR</t>
+          <t>HUC</t>
         </is>
       </c>
       <c r="G326" t="inlineStr">
@@ -13067,16 +13157,16 @@
         </is>
       </c>
       <c r="M326">
-        <v>19526</v>
+        <v>44590</v>
       </c>
     </row>
     <row r="327">
       <c r="A327">
-        <v>1906</v>
+        <v>1905</v>
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>HUC</t>
+          <t>GCL + SPR</t>
         </is>
       </c>
       <c r="G327" t="inlineStr">
@@ -13085,16 +13175,16 @@
         </is>
       </c>
       <c r="M327">
-        <v>19526</v>
+        <v>24440</v>
       </c>
     </row>
     <row r="328">
       <c r="A328">
-        <v>1907</v>
+        <v>1905</v>
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>GCL + SPR</t>
+          <t>HUC</t>
         </is>
       </c>
       <c r="G328" t="inlineStr">
@@ -13103,16 +13193,16 @@
         </is>
       </c>
       <c r="M328">
-        <v>13962</v>
+        <v>24440</v>
       </c>
     </row>
     <row r="329">
       <c r="A329">
-        <v>1907</v>
+        <v>1906</v>
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>HUC</t>
+          <t>GCL + SPR</t>
         </is>
       </c>
       <c r="G329" t="inlineStr">
@@ -13121,16 +13211,16 @@
         </is>
       </c>
       <c r="M329">
-        <v>13962</v>
+        <v>19526</v>
       </c>
     </row>
     <row r="330">
       <c r="A330">
-        <v>1908</v>
+        <v>1906</v>
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>GCL + SPR</t>
+          <t>HUC</t>
         </is>
       </c>
       <c r="G330" t="inlineStr">
@@ -13139,16 +13229,16 @@
         </is>
       </c>
       <c r="M330">
-        <v>6526</v>
+        <v>19526</v>
       </c>
     </row>
     <row r="331">
       <c r="A331">
-        <v>1908</v>
+        <v>1907</v>
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>HUC</t>
+          <t>GCL + SPR</t>
         </is>
       </c>
       <c r="G331" t="inlineStr">
@@ -13157,42 +13247,52 @@
         </is>
       </c>
       <c r="M331">
-        <v>6526</v>
+        <v>13962</v>
       </c>
     </row>
     <row r="332">
       <c r="A332">
-        <v>1909</v>
+        <v>1907</v>
       </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t>GCL + SPR</t>
+          <t>HUC</t>
+        </is>
+      </c>
+      <c r="G332" t="inlineStr">
+        <is>
+          <t>cannery pack</t>
         </is>
       </c>
       <c r="M332">
-        <v>0</v>
+        <v>13962</v>
       </c>
     </row>
     <row r="333">
       <c r="A333">
-        <v>1909</v>
+        <v>1908</v>
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>HUC</t>
+          <t>GCL + SPR</t>
+        </is>
+      </c>
+      <c r="G333" t="inlineStr">
+        <is>
+          <t>cannery pack</t>
         </is>
       </c>
       <c r="M333">
-        <v>0</v>
+        <v>6526</v>
       </c>
     </row>
     <row r="334">
       <c r="A334">
-        <v>1910</v>
+        <v>1908</v>
       </c>
       <c r="B334" t="inlineStr">
         <is>
-          <t>GCL + SPR</t>
+          <t>HUC</t>
         </is>
       </c>
       <c r="G334" t="inlineStr">
@@ -13201,52 +13301,42 @@
         </is>
       </c>
       <c r="M334">
-        <v>36608</v>
+        <v>6526</v>
       </c>
     </row>
     <row r="335">
       <c r="A335">
-        <v>1910</v>
+        <v>1909</v>
       </c>
       <c r="B335" t="inlineStr">
         <is>
-          <t>HUC</t>
-        </is>
-      </c>
-      <c r="G335" t="inlineStr">
-        <is>
-          <t>cannery pack</t>
+          <t>GCL + SPR</t>
         </is>
       </c>
       <c r="M335">
-        <v>36608</v>
+        <v>0</v>
       </c>
     </row>
     <row r="336">
       <c r="A336">
-        <v>1911</v>
+        <v>1909</v>
       </c>
       <c r="B336" t="inlineStr">
         <is>
-          <t>GCL + SPR</t>
-        </is>
-      </c>
-      <c r="G336" t="inlineStr">
-        <is>
-          <t>cannery pack</t>
+          <t>HUC</t>
         </is>
       </c>
       <c r="M336">
-        <v>93847</v>
+        <v>0</v>
       </c>
     </row>
     <row r="337">
       <c r="A337">
-        <v>1911</v>
+        <v>1910</v>
       </c>
       <c r="B337" t="inlineStr">
         <is>
-          <t>HUC</t>
+          <t>GCL + SPR</t>
         </is>
       </c>
       <c r="G337" t="inlineStr">
@@ -13255,55 +13345,70 @@
         </is>
       </c>
       <c r="M337">
-        <v>93847</v>
+        <v>36608</v>
       </c>
     </row>
     <row r="338">
       <c r="A338">
-        <v>1912</v>
+        <v>1910</v>
       </c>
       <c r="B338" t="inlineStr">
         <is>
-          <t>GCL + SPR</t>
+          <t>HUC</t>
+        </is>
+      </c>
+      <c r="G338" t="inlineStr">
+        <is>
+          <t>cannery pack</t>
         </is>
       </c>
       <c r="M338">
-        <v>0</v>
+        <v>36608</v>
       </c>
     </row>
     <row r="339">
       <c r="A339">
-        <v>1912</v>
+        <v>1911</v>
       </c>
       <c r="B339" t="inlineStr">
         <is>
-          <t>HUC</t>
+          <t>GCL + SPR</t>
+        </is>
+      </c>
+      <c r="G339" t="inlineStr">
+        <is>
+          <t>cannery pack</t>
         </is>
       </c>
       <c r="M339">
-        <v>0</v>
+        <v>93847</v>
       </c>
     </row>
     <row r="340">
       <c r="A340">
-        <v>1913</v>
+        <v>1911</v>
       </c>
       <c r="B340" t="inlineStr">
         <is>
-          <t>GCL + SPR</t>
+          <t>HUC</t>
+        </is>
+      </c>
+      <c r="G340" t="inlineStr">
+        <is>
+          <t>cannery pack</t>
         </is>
       </c>
       <c r="M340">
-        <v>0</v>
+        <v>93847</v>
       </c>
     </row>
     <row r="341">
       <c r="A341">
-        <v>1913</v>
+        <v>1912</v>
       </c>
       <c r="B341" t="inlineStr">
         <is>
-          <t>HUC</t>
+          <t>GCL + SPR</t>
         </is>
       </c>
       <c r="M341">
@@ -13312,11 +13417,11 @@
     </row>
     <row r="342">
       <c r="A342">
-        <v>1914</v>
+        <v>1912</v>
       </c>
       <c r="B342" t="inlineStr">
         <is>
-          <t>GCL + SPR</t>
+          <t>HUC</t>
         </is>
       </c>
       <c r="M342">
@@ -13325,11 +13430,11 @@
     </row>
     <row r="343">
       <c r="A343">
-        <v>1914</v>
+        <v>1913</v>
       </c>
       <c r="B343" t="inlineStr">
         <is>
-          <t>HUC</t>
+          <t>GCL + SPR</t>
         </is>
       </c>
       <c r="M343">
@@ -13338,11 +13443,11 @@
     </row>
     <row r="344">
       <c r="A344">
-        <v>1915</v>
+        <v>1913</v>
       </c>
       <c r="B344" t="inlineStr">
         <is>
-          <t>GCL + SPR</t>
+          <t>HUC</t>
         </is>
       </c>
       <c r="M344">
@@ -13351,64 +13456,46 @@
     </row>
     <row r="345">
       <c r="A345">
-        <v>1916</v>
+        <v>1914</v>
       </c>
       <c r="B345" t="inlineStr">
         <is>
           <t>GCL + SPR</t>
         </is>
       </c>
-      <c r="G345" t="inlineStr">
-        <is>
-          <t>cannery pack</t>
-        </is>
-      </c>
       <c r="M345">
-        <v>18005</v>
+        <v>0</v>
       </c>
     </row>
     <row r="346">
       <c r="A346">
-        <v>1917</v>
+        <v>1914</v>
       </c>
       <c r="B346" t="inlineStr">
         <is>
-          <t>GCL + SPR</t>
-        </is>
-      </c>
-      <c r="G346" t="inlineStr">
-        <is>
-          <t>cannery pack</t>
+          <t>HUC</t>
         </is>
       </c>
       <c r="M346">
-        <v>14196</v>
+        <v>0</v>
       </c>
     </row>
     <row r="347">
       <c r="A347">
-        <v>1918</v>
+        <v>1915</v>
       </c>
       <c r="B347" t="inlineStr">
         <is>
           <t>GCL + SPR</t>
         </is>
       </c>
-      <c r="G347" t="inlineStr">
-        <is>
-          <t>cannery pack</t>
-        </is>
-      </c>
       <c r="M347">
-        <v>16354</v>
-      </c>
-      <c r="N347">
-        <v>7000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="348">
       <c r="A348">
-        <v>1919</v>
+        <v>1916</v>
       </c>
       <c r="B348" t="inlineStr">
         <is>
@@ -13421,15 +13508,12 @@
         </is>
       </c>
       <c r="M348">
-        <v>32474</v>
-      </c>
-      <c r="N348">
-        <v>8000</v>
+        <v>18005</v>
       </c>
     </row>
     <row r="349">
       <c r="A349">
-        <v>1920</v>
+        <v>1917</v>
       </c>
       <c r="B349" t="inlineStr">
         <is>
@@ -13442,15 +13526,12 @@
         </is>
       </c>
       <c r="M349">
-        <v>6006</v>
-      </c>
-      <c r="N349">
-        <v>38000</v>
+        <v>14196</v>
       </c>
     </row>
     <row r="350">
       <c r="A350">
-        <v>1921</v>
+        <v>1918</v>
       </c>
       <c r="B350" t="inlineStr">
         <is>
@@ -13463,15 +13544,15 @@
         </is>
       </c>
       <c r="M350">
-        <v>325</v>
+        <v>16354</v>
       </c>
       <c r="N350">
-        <v>1000</v>
+        <v>7000</v>
       </c>
     </row>
     <row r="351">
       <c r="A351">
-        <v>1922</v>
+        <v>1919</v>
       </c>
       <c r="B351" t="inlineStr">
         <is>
@@ -13484,15 +13565,15 @@
         </is>
       </c>
       <c r="M351">
-        <v>12350</v>
+        <v>32474</v>
       </c>
       <c r="N351">
-        <v>70000</v>
+        <v>8000</v>
       </c>
     </row>
     <row r="352">
       <c r="A352">
-        <v>1923</v>
+        <v>1920</v>
       </c>
       <c r="B352" t="inlineStr">
         <is>
@@ -13505,15 +13586,15 @@
         </is>
       </c>
       <c r="M352">
-        <v>1456</v>
+        <v>6006</v>
       </c>
       <c r="N352">
-        <v>90000</v>
+        <v>38000</v>
       </c>
     </row>
     <row r="353">
       <c r="A353">
-        <v>1924</v>
+        <v>1921</v>
       </c>
       <c r="B353" t="inlineStr">
         <is>
@@ -13526,15 +13607,15 @@
         </is>
       </c>
       <c r="M353">
-        <v>2964</v>
+        <v>325</v>
       </c>
       <c r="N353">
-        <v>120000</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="354">
       <c r="A354">
-        <v>1925</v>
+        <v>1922</v>
       </c>
       <c r="B354" t="inlineStr">
         <is>
@@ -13547,87 +13628,78 @@
         </is>
       </c>
       <c r="M354">
-        <v>16081</v>
+        <v>12350</v>
       </c>
       <c r="N354">
-        <v>80000</v>
+        <v>70000</v>
       </c>
     </row>
     <row r="355">
       <c r="A355">
-        <v>1926</v>
+        <v>1923</v>
       </c>
       <c r="B355" t="inlineStr">
         <is>
           <t>GCL + SPR</t>
         </is>
       </c>
-      <c r="E355">
-        <v>10000</v>
-      </c>
       <c r="G355" t="inlineStr">
         <is>
-          <t>commercial catch records</t>
+          <t>cannery pack</t>
         </is>
       </c>
       <c r="M355">
-        <v>45412</v>
+        <v>1456</v>
       </c>
       <c r="N355">
-        <v>75695</v>
+        <v>90000</v>
       </c>
     </row>
     <row r="356">
       <c r="A356">
-        <v>1927</v>
+        <v>1924</v>
       </c>
       <c r="B356" t="inlineStr">
         <is>
           <t>GCL + SPR</t>
         </is>
       </c>
-      <c r="E356">
-        <v>65400</v>
-      </c>
       <c r="G356" t="inlineStr">
         <is>
-          <t>commercial catch records</t>
+          <t>cannery pack</t>
         </is>
       </c>
       <c r="M356">
-        <v>91069</v>
+        <v>2964</v>
       </c>
       <c r="N356">
-        <v>70000</v>
+        <v>120000</v>
       </c>
     </row>
     <row r="357">
       <c r="A357">
-        <v>1928</v>
+        <v>1925</v>
       </c>
       <c r="B357" t="inlineStr">
         <is>
           <t>GCL + SPR</t>
         </is>
       </c>
-      <c r="E357">
-        <v>23000</v>
-      </c>
       <c r="G357" t="inlineStr">
         <is>
-          <t>commercial catch records</t>
+          <t>cannery pack</t>
         </is>
       </c>
       <c r="M357">
-        <v>38000</v>
+        <v>16081</v>
       </c>
       <c r="N357">
-        <v>70000</v>
+        <v>80000</v>
       </c>
     </row>
     <row r="358">
       <c r="A358">
-        <v>1929</v>
+        <v>1926</v>
       </c>
       <c r="B358" t="inlineStr">
         <is>
@@ -13635,7 +13707,7 @@
         </is>
       </c>
       <c r="E358">
-        <v>18000</v>
+        <v>10000</v>
       </c>
       <c r="G358" t="inlineStr">
         <is>
@@ -13643,15 +13715,15 @@
         </is>
       </c>
       <c r="M358">
-        <v>18000</v>
+        <v>45412</v>
       </c>
       <c r="N358">
-        <v>138018</v>
+        <v>75695</v>
       </c>
     </row>
     <row r="359">
       <c r="A359">
-        <v>1930</v>
+        <v>1927</v>
       </c>
       <c r="B359" t="inlineStr">
         <is>
@@ -13659,7 +13731,7 @@
         </is>
       </c>
       <c r="E359">
-        <v>48000</v>
+        <v>65400</v>
       </c>
       <c r="G359" t="inlineStr">
         <is>
@@ -13667,15 +13739,15 @@
         </is>
       </c>
       <c r="M359">
-        <v>58600</v>
+        <v>91069</v>
       </c>
       <c r="N359">
-        <v>49501</v>
+        <v>70000</v>
       </c>
     </row>
     <row r="360">
       <c r="A360">
-        <v>1931</v>
+        <v>1928</v>
       </c>
       <c r="B360" t="inlineStr">
         <is>
@@ -13683,7 +13755,7 @@
         </is>
       </c>
       <c r="E360">
-        <v>39000</v>
+        <v>23000</v>
       </c>
       <c r="G360" t="inlineStr">
         <is>
@@ -13691,15 +13763,15 @@
         </is>
       </c>
       <c r="M360">
-        <v>59260</v>
+        <v>38000</v>
       </c>
       <c r="N360">
-        <v>56920</v>
+        <v>70000</v>
       </c>
     </row>
     <row r="361">
       <c r="A361">
-        <v>1932</v>
+        <v>1929</v>
       </c>
       <c r="B361" t="inlineStr">
         <is>
@@ -13707,7 +13779,7 @@
         </is>
       </c>
       <c r="E361">
-        <v>77000</v>
+        <v>18000</v>
       </c>
       <c r="G361" t="inlineStr">
         <is>
@@ -13715,15 +13787,15 @@
         </is>
       </c>
       <c r="M361">
-        <v>105000</v>
+        <v>18000</v>
       </c>
       <c r="N361">
-        <v>37472</v>
+        <v>138018</v>
       </c>
     </row>
     <row r="362">
       <c r="A362">
-        <v>1933</v>
+        <v>1930</v>
       </c>
       <c r="B362" t="inlineStr">
         <is>
@@ -13731,7 +13803,7 @@
         </is>
       </c>
       <c r="E362">
-        <v>60000</v>
+        <v>48000</v>
       </c>
       <c r="G362" t="inlineStr">
         <is>
@@ -13739,15 +13811,15 @@
         </is>
       </c>
       <c r="M362">
-        <v>80500</v>
+        <v>58600</v>
       </c>
       <c r="N362">
-        <v>9206</v>
+        <v>49501</v>
       </c>
     </row>
     <row r="363">
       <c r="A363">
-        <v>1934</v>
+        <v>1931</v>
       </c>
       <c r="B363" t="inlineStr">
         <is>
@@ -13755,7 +13827,7 @@
         </is>
       </c>
       <c r="E363">
-        <v>75000</v>
+        <v>39000</v>
       </c>
       <c r="G363" t="inlineStr">
         <is>
@@ -13763,78 +13835,87 @@
         </is>
       </c>
       <c r="M363">
-        <v>81500</v>
+        <v>59260</v>
       </c>
       <c r="N363">
-        <v>19858</v>
+        <v>56920</v>
       </c>
     </row>
     <row r="364">
       <c r="A364">
-        <v>1935</v>
+        <v>1932</v>
       </c>
       <c r="B364" t="inlineStr">
         <is>
           <t>GCL + SPR</t>
         </is>
       </c>
+      <c r="E364">
+        <v>77000</v>
+      </c>
       <c r="G364" t="inlineStr">
         <is>
           <t>commercial catch records</t>
         </is>
       </c>
       <c r="M364">
-        <v>71020</v>
+        <v>105000</v>
       </c>
       <c r="N364">
-        <v>50953</v>
+        <v>37472</v>
       </c>
     </row>
     <row r="365">
       <c r="A365">
-        <v>1936</v>
+        <v>1933</v>
       </c>
       <c r="B365" t="inlineStr">
         <is>
           <t>GCL + SPR</t>
         </is>
       </c>
+      <c r="E365">
+        <v>60000</v>
+      </c>
       <c r="G365" t="inlineStr">
         <is>
           <t>commercial catch records</t>
         </is>
       </c>
       <c r="M365">
-        <v>94580</v>
+        <v>80500</v>
       </c>
       <c r="N365">
-        <v>14206</v>
+        <v>9206</v>
       </c>
     </row>
     <row r="366">
       <c r="A366">
-        <v>1937</v>
+        <v>1934</v>
       </c>
       <c r="B366" t="inlineStr">
         <is>
           <t>GCL + SPR</t>
         </is>
       </c>
+      <c r="E366">
+        <v>75000</v>
+      </c>
       <c r="G366" t="inlineStr">
         <is>
           <t>commercial catch records</t>
         </is>
       </c>
       <c r="M366">
-        <v>61000</v>
+        <v>81500</v>
       </c>
       <c r="N366">
-        <v>45365</v>
+        <v>19858</v>
       </c>
     </row>
     <row r="367">
       <c r="A367">
-        <v>1938</v>
+        <v>1935</v>
       </c>
       <c r="B367" t="inlineStr">
         <is>
@@ -13847,15 +13928,15 @@
         </is>
       </c>
       <c r="M367">
-        <v>47300</v>
+        <v>71020</v>
       </c>
       <c r="N367">
-        <v>15894</v>
+        <v>50953</v>
       </c>
     </row>
     <row r="368">
       <c r="A368">
-        <v>1939</v>
+        <v>1936</v>
       </c>
       <c r="B368" t="inlineStr">
         <is>
@@ -13868,15 +13949,15 @@
         </is>
       </c>
       <c r="M368">
-        <v>51000</v>
+        <v>94580</v>
       </c>
       <c r="N368">
-        <v>17119</v>
+        <v>14206</v>
       </c>
     </row>
     <row r="369">
       <c r="A369">
-        <v>1940</v>
+        <v>1937</v>
       </c>
       <c r="B369" t="inlineStr">
         <is>
@@ -13889,15 +13970,15 @@
         </is>
       </c>
       <c r="M369">
-        <v>26580</v>
+        <v>61000</v>
       </c>
       <c r="N369">
-        <v>62936</v>
+        <v>45365</v>
       </c>
     </row>
     <row r="370">
       <c r="A370">
-        <v>1941</v>
+        <v>1938</v>
       </c>
       <c r="B370" t="inlineStr">
         <is>
@@ -13910,15 +13991,15 @@
         </is>
       </c>
       <c r="M370">
-        <v>25000</v>
+        <v>47300</v>
       </c>
       <c r="N370">
-        <v>16625</v>
+        <v>15894</v>
       </c>
     </row>
     <row r="371">
       <c r="A371">
-        <v>1942</v>
+        <v>1939</v>
       </c>
       <c r="B371" t="inlineStr">
         <is>
@@ -13931,15 +14012,15 @@
         </is>
       </c>
       <c r="M371">
-        <v>29200</v>
+        <v>51000</v>
       </c>
       <c r="N371">
-        <v>22823</v>
+        <v>17119</v>
       </c>
     </row>
     <row r="372">
       <c r="A372">
-        <v>1943</v>
+        <v>1940</v>
       </c>
       <c r="B372" t="inlineStr">
         <is>
@@ -13952,15 +14033,15 @@
         </is>
       </c>
       <c r="M372">
-        <v>38860</v>
+        <v>26580</v>
       </c>
       <c r="N372">
-        <v>10421</v>
+        <v>62936</v>
       </c>
     </row>
     <row r="373">
       <c r="A373">
-        <v>1944</v>
+        <v>1941</v>
       </c>
       <c r="B373" t="inlineStr">
         <is>
@@ -13973,15 +14054,15 @@
         </is>
       </c>
       <c r="M373">
-        <v>14600</v>
+        <v>25000</v>
       </c>
       <c r="N373">
-        <v>9537</v>
+        <v>16625</v>
       </c>
     </row>
     <row r="374">
       <c r="A374">
-        <v>1945</v>
+        <v>1942</v>
       </c>
       <c r="B374" t="inlineStr">
         <is>
@@ -13994,15 +14075,15 @@
         </is>
       </c>
       <c r="M374">
-        <v>11800</v>
+        <v>29200</v>
       </c>
       <c r="N374">
-        <v>40245</v>
+        <v>22823</v>
       </c>
     </row>
     <row r="375">
       <c r="A375">
-        <v>1946</v>
+        <v>1943</v>
       </c>
       <c r="B375" t="inlineStr">
         <is>
@@ -14015,15 +14096,15 @@
         </is>
       </c>
       <c r="M375">
-        <v>13980</v>
+        <v>38860</v>
       </c>
       <c r="N375">
-        <v>19986</v>
+        <v>10421</v>
       </c>
     </row>
     <row r="376">
       <c r="A376">
-        <v>1947</v>
+        <v>1944</v>
       </c>
       <c r="B376" t="inlineStr">
         <is>
@@ -14036,15 +14117,15 @@
         </is>
       </c>
       <c r="M376">
-        <v>5440</v>
+        <v>14600</v>
       </c>
       <c r="N376">
-        <v>12900</v>
+        <v>9537</v>
       </c>
     </row>
     <row r="377">
       <c r="A377">
-        <v>1948</v>
+        <v>1945</v>
       </c>
       <c r="B377" t="inlineStr">
         <is>
@@ -14057,15 +14138,15 @@
         </is>
       </c>
       <c r="M377">
-        <v>9560</v>
+        <v>11800</v>
       </c>
       <c r="N377">
-        <v>11167</v>
+        <v>40245</v>
       </c>
     </row>
     <row r="378">
       <c r="A378">
-        <v>1949</v>
+        <v>1946</v>
       </c>
       <c r="B378" t="inlineStr">
         <is>
@@ -14078,15 +14159,15 @@
         </is>
       </c>
       <c r="M378">
-        <v>35720</v>
+        <v>13980</v>
       </c>
       <c r="N378">
-        <v>80418</v>
+        <v>19986</v>
       </c>
     </row>
     <row r="379">
       <c r="A379">
-        <v>1950</v>
+        <v>1947</v>
       </c>
       <c r="B379" t="inlineStr">
         <is>
@@ -14099,15 +14180,15 @@
         </is>
       </c>
       <c r="M379">
-        <v>55190</v>
+        <v>5440</v>
       </c>
       <c r="N379">
-        <v>44000</v>
+        <v>12900</v>
       </c>
     </row>
     <row r="380">
       <c r="A380">
-        <v>1951</v>
+        <v>1948</v>
       </c>
       <c r="B380" t="inlineStr">
         <is>
@@ -14120,15 +14201,15 @@
         </is>
       </c>
       <c r="M380">
-        <v>76018</v>
+        <v>9560</v>
       </c>
       <c r="N380">
-        <v>89000</v>
+        <v>11167</v>
       </c>
     </row>
     <row r="381">
       <c r="A381">
-        <v>1952</v>
+        <v>1949</v>
       </c>
       <c r="B381" t="inlineStr">
         <is>
@@ -14141,15 +14222,15 @@
         </is>
       </c>
       <c r="M381">
-        <v>50094</v>
+        <v>35720</v>
       </c>
       <c r="N381">
-        <v>36000</v>
+        <v>80418</v>
       </c>
     </row>
     <row r="382">
       <c r="A382">
-        <v>1953</v>
+        <v>1950</v>
       </c>
       <c r="B382" t="inlineStr">
         <is>
@@ -14162,15 +14243,15 @@
         </is>
       </c>
       <c r="M382">
-        <v>76328</v>
+        <v>55190</v>
       </c>
       <c r="N382">
-        <v>64000</v>
+        <v>44000</v>
       </c>
     </row>
     <row r="383">
       <c r="A383">
-        <v>1954</v>
+        <v>1951</v>
       </c>
       <c r="B383" t="inlineStr">
         <is>
@@ -14183,15 +14264,15 @@
         </is>
       </c>
       <c r="M383">
-        <v>38405</v>
+        <v>76018</v>
       </c>
       <c r="N383">
-        <v>65000</v>
+        <v>89000</v>
       </c>
     </row>
     <row r="384">
       <c r="A384">
-        <v>1955</v>
+        <v>1952</v>
       </c>
       <c r="B384" t="inlineStr">
         <is>
@@ -14204,15 +14285,15 @@
         </is>
       </c>
       <c r="M384">
-        <v>28714</v>
+        <v>50094</v>
       </c>
       <c r="N384">
-        <v>39000</v>
+        <v>36000</v>
       </c>
     </row>
     <row r="385">
       <c r="A385">
-        <v>1956</v>
+        <v>1953</v>
       </c>
       <c r="B385" t="inlineStr">
         <is>
@@ -14225,15 +14306,15 @@
         </is>
       </c>
       <c r="M385">
-        <v>8934</v>
+        <v>76328</v>
       </c>
       <c r="N385">
-        <v>17000</v>
+        <v>64000</v>
       </c>
     </row>
     <row r="386">
       <c r="A386">
-        <v>1957</v>
+        <v>1954</v>
       </c>
       <c r="B386" t="inlineStr">
         <is>
@@ -14246,15 +14327,15 @@
         </is>
       </c>
       <c r="M386">
-        <v>11749</v>
+        <v>38405</v>
       </c>
       <c r="N386">
-        <v>147000</v>
+        <v>65000</v>
       </c>
     </row>
     <row r="387">
       <c r="A387">
-        <v>1958</v>
+        <v>1955</v>
       </c>
       <c r="B387" t="inlineStr">
         <is>
@@ -14267,15 +14348,15 @@
         </is>
       </c>
       <c r="M387">
-        <v>8296</v>
+        <v>28714</v>
       </c>
       <c r="N387">
-        <v>54000</v>
+        <v>39000</v>
       </c>
     </row>
     <row r="388">
       <c r="A388">
-        <v>1959</v>
+        <v>1956</v>
       </c>
       <c r="B388" t="inlineStr">
         <is>
@@ -14288,15 +14369,15 @@
         </is>
       </c>
       <c r="M388">
-        <v>6966</v>
+        <v>8934</v>
       </c>
       <c r="N388">
-        <v>54000</v>
+        <v>17000</v>
       </c>
     </row>
     <row r="389">
       <c r="A389">
-        <v>1960</v>
+        <v>1957</v>
       </c>
       <c r="B389" t="inlineStr">
         <is>
@@ -14309,15 +14390,15 @@
         </is>
       </c>
       <c r="M389">
-        <v>9144</v>
+        <v>11749</v>
       </c>
       <c r="N389">
-        <v>50000</v>
+        <v>147000</v>
       </c>
     </row>
     <row r="390">
       <c r="A390">
-        <v>1961</v>
+        <v>1958</v>
       </c>
       <c r="B390" t="inlineStr">
         <is>
@@ -14330,15 +14411,15 @@
         </is>
       </c>
       <c r="M390">
-        <v>21864</v>
+        <v>8296</v>
       </c>
       <c r="N390">
-        <v>50000</v>
+        <v>54000</v>
       </c>
     </row>
     <row r="391">
       <c r="A391">
-        <v>1962</v>
+        <v>1959</v>
       </c>
       <c r="B391" t="inlineStr">
         <is>
@@ -14351,15 +14432,15 @@
         </is>
       </c>
       <c r="M391">
-        <v>16299</v>
+        <v>6966</v>
       </c>
       <c r="N391">
-        <v>58000</v>
+        <v>54000</v>
       </c>
     </row>
     <row r="392">
       <c r="A392">
-        <v>1963</v>
+        <v>1960</v>
       </c>
       <c r="B392" t="inlineStr">
         <is>
@@ -14372,7 +14453,7 @@
         </is>
       </c>
       <c r="M392">
-        <v>11065</v>
+        <v>9144</v>
       </c>
       <c r="N392">
         <v>50000</v>
@@ -14380,7 +14461,7 @@
     </row>
     <row r="393">
       <c r="A393">
-        <v>1964</v>
+        <v>1961</v>
       </c>
       <c r="B393" t="inlineStr">
         <is>
@@ -14393,15 +14474,15 @@
         </is>
       </c>
       <c r="M393">
-        <v>11218</v>
+        <v>21864</v>
       </c>
       <c r="N393">
-        <v>113000</v>
+        <v>50000</v>
       </c>
     </row>
     <row r="394">
       <c r="A394">
-        <v>1965</v>
+        <v>1962</v>
       </c>
       <c r="B394" t="inlineStr">
         <is>
@@ -14414,15 +14495,15 @@
         </is>
       </c>
       <c r="M394">
-        <v>17657</v>
+        <v>16299</v>
       </c>
       <c r="N394">
-        <v>56000</v>
+        <v>58000</v>
       </c>
     </row>
     <row r="395">
       <c r="A395">
-        <v>1966</v>
+        <v>1963</v>
       </c>
       <c r="B395" t="inlineStr">
         <is>
@@ -14435,15 +14516,15 @@
         </is>
       </c>
       <c r="M395">
-        <v>29151</v>
+        <v>11065</v>
       </c>
       <c r="N395">
-        <v>176000</v>
+        <v>50000</v>
       </c>
     </row>
     <row r="396">
       <c r="A396">
-        <v>1967</v>
+        <v>1964</v>
       </c>
       <c r="B396" t="inlineStr">
         <is>
@@ -14456,15 +14537,15 @@
         </is>
       </c>
       <c r="M396">
-        <v>31022</v>
+        <v>11218</v>
       </c>
       <c r="N396">
-        <v>135500</v>
+        <v>113000</v>
       </c>
     </row>
     <row r="397">
       <c r="A397">
-        <v>1968</v>
+        <v>1965</v>
       </c>
       <c r="B397" t="inlineStr">
         <is>
@@ -14477,15 +14558,15 @@
         </is>
       </c>
       <c r="M397">
-        <v>28828</v>
+        <v>17657</v>
       </c>
       <c r="N397">
-        <v>137600</v>
+        <v>56000</v>
       </c>
     </row>
     <row r="398">
       <c r="A398">
-        <v>1969</v>
+        <v>1966</v>
       </c>
       <c r="B398" t="inlineStr">
         <is>
@@ -14498,15 +14579,15 @@
         </is>
       </c>
       <c r="M398">
-        <v>56787</v>
+        <v>29151</v>
       </c>
       <c r="N398">
-        <v>114900</v>
+        <v>176000</v>
       </c>
     </row>
     <row r="399">
       <c r="A399">
-        <v>1970</v>
+        <v>1967</v>
       </c>
       <c r="B399" t="inlineStr">
         <is>
@@ -14519,15 +14600,15 @@
         </is>
       </c>
       <c r="M399">
-        <v>89092</v>
+        <v>31022</v>
       </c>
       <c r="N399">
-        <v>42100</v>
+        <v>135500</v>
       </c>
     </row>
     <row r="400">
       <c r="A400">
-        <v>1971</v>
+        <v>1968</v>
       </c>
       <c r="B400" t="inlineStr">
         <is>
@@ -14540,15 +14621,15 @@
         </is>
       </c>
       <c r="M400">
-        <v>51875</v>
+        <v>28828</v>
       </c>
       <c r="N400">
-        <v>71700</v>
+        <v>137600</v>
       </c>
     </row>
     <row r="401">
       <c r="A401">
-        <v>1972</v>
+        <v>1969</v>
       </c>
       <c r="B401" t="inlineStr">
         <is>
@@ -14561,15 +14642,15 @@
         </is>
       </c>
       <c r="M401">
-        <v>225718</v>
+        <v>56787</v>
       </c>
       <c r="N401">
-        <v>139400</v>
+        <v>114900</v>
       </c>
     </row>
     <row r="402">
       <c r="A402">
-        <v>1973</v>
+        <v>1970</v>
       </c>
       <c r="B402" t="inlineStr">
         <is>
@@ -14582,15 +14663,15 @@
         </is>
       </c>
       <c r="M402">
-        <v>451615</v>
+        <v>89092</v>
       </c>
       <c r="N402">
-        <v>301700</v>
+        <v>42100</v>
       </c>
     </row>
     <row r="403">
       <c r="A403">
-        <v>1974</v>
+        <v>1971</v>
       </c>
       <c r="B403" t="inlineStr">
         <is>
@@ -14603,15 +14684,15 @@
         </is>
       </c>
       <c r="M403">
-        <v>427790</v>
+        <v>51875</v>
       </c>
       <c r="N403">
-        <v>98100</v>
+        <v>71700</v>
       </c>
     </row>
     <row r="404">
       <c r="A404">
-        <v>1975</v>
+        <v>1972</v>
       </c>
       <c r="B404" t="inlineStr">
         <is>
@@ -14624,30 +14705,93 @@
         </is>
       </c>
       <c r="M404">
-        <v>440977</v>
+        <v>225718</v>
       </c>
       <c r="N404">
-        <v>195600</v>
+        <v>139400</v>
       </c>
     </row>
     <row r="405">
       <c r="A405">
+        <v>1973</v>
+      </c>
+      <c r="B405" t="inlineStr">
+        <is>
+          <t>GCL + SPR</t>
+        </is>
+      </c>
+      <c r="G405" t="inlineStr">
+        <is>
+          <t>commercial catch records</t>
+        </is>
+      </c>
+      <c r="M405">
+        <v>451615</v>
+      </c>
+      <c r="N405">
+        <v>301700</v>
+      </c>
+    </row>
+    <row r="406">
+      <c r="A406">
+        <v>1974</v>
+      </c>
+      <c r="B406" t="inlineStr">
+        <is>
+          <t>GCL + SPR</t>
+        </is>
+      </c>
+      <c r="G406" t="inlineStr">
+        <is>
+          <t>commercial catch records</t>
+        </is>
+      </c>
+      <c r="M406">
+        <v>427790</v>
+      </c>
+      <c r="N406">
+        <v>98100</v>
+      </c>
+    </row>
+    <row r="407">
+      <c r="A407">
+        <v>1975</v>
+      </c>
+      <c r="B407" t="inlineStr">
+        <is>
+          <t>GCL + SPR</t>
+        </is>
+      </c>
+      <c r="G407" t="inlineStr">
+        <is>
+          <t>commercial catch records</t>
+        </is>
+      </c>
+      <c r="M407">
+        <v>440977</v>
+      </c>
+      <c r="N407">
+        <v>195600</v>
+      </c>
+    </row>
+    <row r="408">
+      <c r="A408">
         <v>1976</v>
       </c>
-      <c r="B405" t="inlineStr">
+      <c r="B408" t="inlineStr">
         <is>
           <t>GCL + SPR</t>
         </is>
       </c>
-      <c r="G405" t="inlineStr">
+      <c r="G408" t="inlineStr">
         <is>
           <t>commercial catch records</t>
         </is>
       </c>
-      <c r="M405">
+      <c r="M408">
         <v>1408490</v>
       </c>
-      <c r="N405">
+      <c r="N408">
         <v>151800</v>
       </c>
     </row>

--- a/3. outputs/Total return time series/Barkley Sockeye total annual returns by CU_collated.xlsx
+++ b/3. outputs/Total return time series/Barkley Sockeye total annual returns by CU_collated.xlsx
@@ -4975,7 +4975,7 @@
         <v>15964</v>
       </c>
       <c r="E112">
-        <v>4923</v>
+        <v>4641</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -5004,7 +5004,7 @@
         <v>0</v>
       </c>
       <c r="M112">
-        <v>294097</v>
+        <v>293328</v>
       </c>
       <c r="N112">
         <v>569894</v>
@@ -13005,7 +13005,7 @@
         <v>447617</v>
       </c>
       <c r="E321">
-        <v>233609</v>
+        <v>233151</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -13034,7 +13034,7 @@
         <v>0</v>
       </c>
       <c r="M321">
-        <v>294097</v>
+        <v>293328</v>
       </c>
       <c r="N321">
         <v>569894</v>
@@ -13053,7 +13053,7 @@
         <v>106313</v>
       </c>
       <c r="E322">
-        <v>55565</v>
+        <v>55536</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -13082,7 +13082,7 @@
         <v>0</v>
       </c>
       <c r="M322">
-        <v>294097</v>
+        <v>293328</v>
       </c>
       <c r="N322">
         <v>569894</v>
